--- a/downloads/tamil-nadu.xlsx
+++ b/downloads/tamil-nadu.xlsx
@@ -852,7 +852,7 @@
         <v>1601</v>
       </c>
       <c r="I2" t="n">
-        <v>14.89</v>
+        <v>14.8919</v>
       </c>
       <c r="J2" t="n">
         <v>242558</v>
@@ -864,7 +864,7 @@
         <v>33397</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72</v>
+        <v>11.7182</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>232522</v>
       </c>
       <c r="R2" t="n">
-        <v>92.42</v>
+        <v>92.4162</v>
       </c>
       <c r="S2" t="n">
         <v>25452</v>
@@ -942,7 +942,7 @@
         <v>2280</v>
       </c>
       <c r="I3" t="n">
-        <v>12.03</v>
+        <v>12.0333</v>
       </c>
       <c r="J3" t="n">
         <v>239141</v>
@@ -954,7 +954,7 @@
         <v>22937</v>
       </c>
       <c r="M3" t="n">
-        <v>8.44</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>226819</v>
       </c>
       <c r="R3" t="n">
-        <v>91.12</v>
+        <v>91.1223</v>
       </c>
       <c r="S3" t="n">
         <v>20349</v>
@@ -1032,7 +1032,7 @@
         <v>1462</v>
       </c>
       <c r="I4" t="n">
-        <v>10.81</v>
+        <v>10.8149</v>
       </c>
       <c r="J4" t="n">
         <v>252154</v>
@@ -1044,7 +1044,7 @@
         <v>22647</v>
       </c>
       <c r="M4" t="n">
-        <v>8.01</v>
+        <v>8.0101</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>238798</v>
       </c>
       <c r="R4" t="n">
-        <v>91.81999999999999</v>
+        <v>91.81570000000001</v>
       </c>
       <c r="S4" t="n">
         <v>19042</v>
@@ -1122,7 +1122,7 @@
         <v>1511</v>
       </c>
       <c r="I5" t="n">
-        <v>12.77</v>
+        <v>12.7711</v>
       </c>
       <c r="J5" t="n">
         <v>238818</v>
@@ -1134,7 +1134,7 @@
         <v>25132</v>
       </c>
       <c r="M5" t="n">
-        <v>9.18</v>
+        <v>9.179500000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>226428</v>
       </c>
       <c r="R5" t="n">
-        <v>91.06</v>
+        <v>91.0626</v>
       </c>
       <c r="S5" t="n">
         <v>20724</v>
@@ -1212,7 +1212,7 @@
         <v>2518</v>
       </c>
       <c r="I6" t="n">
-        <v>11.87</v>
+        <v>11.8676</v>
       </c>
       <c r="J6" t="n">
         <v>348034</v>
@@ -1224,7 +1224,7 @@
         <v>31211</v>
       </c>
       <c r="M6" t="n">
-        <v>7.9</v>
+        <v>7.9035</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>308894</v>
       </c>
       <c r="R6" t="n">
-        <v>84.93000000000001</v>
+        <v>84.93380000000001</v>
       </c>
       <c r="S6" t="n">
         <v>23905</v>
@@ -1302,7 +1302,7 @@
         <v>3041</v>
       </c>
       <c r="I7" t="n">
-        <v>14.45</v>
+        <v>14.4548</v>
       </c>
       <c r="J7" t="n">
         <v>402693</v>
@@ -1314,7 +1314,7 @@
         <v>41965</v>
       </c>
       <c r="M7" t="n">
-        <v>8.91</v>
+        <v>8.9147</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>346005</v>
       </c>
       <c r="R7" t="n">
-        <v>80.7</v>
+        <v>80.69670000000001</v>
       </c>
       <c r="S7" t="n">
         <v>41583</v>
@@ -1392,7 +1392,7 @@
         <v>1521</v>
       </c>
       <c r="I8" t="n">
-        <v>26.51</v>
+        <v>26.5074</v>
       </c>
       <c r="J8" t="n">
         <v>325407</v>
@@ -1404,7 +1404,7 @@
         <v>78744</v>
       </c>
       <c r="M8" t="n">
-        <v>17.78</v>
+        <v>17.7842</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>293692</v>
       </c>
       <c r="R8" t="n">
-        <v>80.68000000000001</v>
+        <v>80.6777</v>
       </c>
       <c r="S8" t="n">
         <v>85032</v>
@@ -1482,7 +1482,7 @@
         <v>1484</v>
       </c>
       <c r="I9" t="n">
-        <v>18.66</v>
+        <v>18.6567</v>
       </c>
       <c r="J9" t="n">
         <v>304511</v>
@@ -1494,7 +1494,7 @@
         <v>43873</v>
       </c>
       <c r="M9" t="n">
-        <v>11.72</v>
+        <v>11.7197</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>259986</v>
       </c>
       <c r="R9" t="n">
-        <v>78.67</v>
+        <v>78.6692</v>
       </c>
       <c r="S9" t="n">
         <v>46982</v>
@@ -1572,7 +1572,7 @@
         <v>3156</v>
       </c>
       <c r="I10" t="n">
-        <v>22.08</v>
+        <v>22.0842</v>
       </c>
       <c r="J10" t="n">
         <v>386327</v>
@@ -1584,7 +1584,7 @@
         <v>75225</v>
       </c>
       <c r="M10" t="n">
-        <v>15.17</v>
+        <v>15.1717</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>361998</v>
       </c>
       <c r="R10" t="n">
-        <v>86.06999999999999</v>
+        <v>86.0668</v>
       </c>
       <c r="S10" t="n">
         <v>77008</v>
@@ -1662,7 +1662,7 @@
         <v>1863</v>
       </c>
       <c r="I11" t="n">
-        <v>23.24</v>
+        <v>23.2413</v>
       </c>
       <c r="J11" t="n">
         <v>222806</v>
@@ -1674,7 +1674,7 @@
         <v>49682</v>
       </c>
       <c r="M11" t="n">
-        <v>17.12</v>
+        <v>17.1159</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>207088</v>
       </c>
       <c r="R11" t="n">
-        <v>86.08</v>
+        <v>86.0765</v>
       </c>
       <c r="S11" t="n">
         <v>48993</v>
@@ -1752,7 +1752,7 @@
         <v>955</v>
       </c>
       <c r="I12" t="n">
-        <v>24.19</v>
+        <v>24.1916</v>
       </c>
       <c r="J12" t="n">
         <v>178356</v>
@@ -1764,7 +1764,7 @@
         <v>39416</v>
       </c>
       <c r="M12" t="n">
-        <v>16.75</v>
+        <v>16.7534</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>1337</v>
       </c>
       <c r="I13" t="n">
-        <v>32.72</v>
+        <v>32.7181</v>
       </c>
       <c r="J13" t="n">
         <v>200181</v>
@@ -1854,7 +1854,7 @@
         <v>74734</v>
       </c>
       <c r="M13" t="n">
-        <v>25.12</v>
+        <v>25.1185</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>204384</v>
       </c>
       <c r="R13" t="n">
-        <v>91.73999999999999</v>
+        <v>91.7376</v>
       </c>
       <c r="S13" t="n">
         <v>78067</v>
@@ -1932,7 +1932,7 @@
         <v>1567</v>
       </c>
       <c r="I14" t="n">
-        <v>35.72</v>
+        <v>35.7168</v>
       </c>
       <c r="J14" t="n">
         <v>186841</v>
@@ -1944,7 +1944,7 @@
         <v>83402</v>
       </c>
       <c r="M14" t="n">
-        <v>28.69</v>
+        <v>28.6947</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>184051</v>
       </c>
       <c r="R14" t="n">
-        <v>88.81</v>
+        <v>88.8058</v>
       </c>
       <c r="S14" t="n">
         <v>80652</v>
@@ -2022,7 +2022,7 @@
         <v>849</v>
       </c>
       <c r="I15" t="n">
-        <v>40.65</v>
+        <v>40.6544</v>
       </c>
       <c r="J15" t="n">
         <v>142706</v>
@@ -2034,7 +2034,7 @@
         <v>80702</v>
       </c>
       <c r="M15" t="n">
-        <v>33.56</v>
+        <v>33.5607</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>141452</v>
       </c>
       <c r="R15" t="n">
-        <v>88.54000000000001</v>
+        <v>88.5381</v>
       </c>
       <c r="S15" t="n">
         <v>79407</v>
@@ -2112,7 +2112,7 @@
         <v>1869</v>
       </c>
       <c r="I16" t="n">
-        <v>26.41</v>
+        <v>26.4091</v>
       </c>
       <c r="J16" t="n">
         <v>164528</v>
@@ -2124,7 +2124,7 @@
         <v>44778</v>
       </c>
       <c r="M16" t="n">
-        <v>20.03</v>
+        <v>20.0285</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>143903</v>
       </c>
       <c r="R16" t="n">
-        <v>80.48999999999999</v>
+        <v>80.4858</v>
       </c>
       <c r="S16" t="n">
         <v>40025</v>
@@ -2202,7 +2202,7 @@
         <v>1089</v>
       </c>
       <c r="I17" t="n">
-        <v>37.91</v>
+        <v>37.9095</v>
       </c>
       <c r="J17" t="n">
         <v>122607</v>
@@ -2214,7 +2214,7 @@
         <v>62586</v>
       </c>
       <c r="M17" t="n">
-        <v>31.69</v>
+        <v>31.6947</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>119738</v>
       </c>
       <c r="R17" t="n">
-        <v>88.77</v>
+        <v>88.7744</v>
       </c>
       <c r="S17" t="n">
         <v>57468</v>
@@ -2292,7 +2292,7 @@
         <v>1378</v>
       </c>
       <c r="I18" t="n">
-        <v>26.04</v>
+        <v>26.0409</v>
       </c>
       <c r="J18" t="n">
         <v>146865</v>
@@ -2304,7 +2304,7 @@
         <v>41645</v>
       </c>
       <c r="M18" t="n">
-        <v>20.97</v>
+        <v>20.9718</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>127356</v>
       </c>
       <c r="R18" t="n">
-        <v>81.15000000000001</v>
+        <v>81.1541</v>
       </c>
       <c r="S18" t="n">
         <v>33513</v>
@@ -2382,7 +2382,7 @@
         <v>1709</v>
       </c>
       <c r="I19" t="n">
-        <v>38.72</v>
+        <v>38.7178</v>
       </c>
       <c r="J19" t="n">
         <v>110517</v>
@@ -2394,7 +2394,7 @@
         <v>63445</v>
       </c>
       <c r="M19" t="n">
-        <v>35.18</v>
+        <v>35.1806</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>99622</v>
       </c>
       <c r="R19" t="n">
-        <v>85.22</v>
+        <v>85.22280000000001</v>
       </c>
       <c r="S19" t="n">
         <v>52810</v>
@@ -2472,7 +2472,7 @@
         <v>1230</v>
       </c>
       <c r="I20" t="n">
-        <v>37.17</v>
+        <v>37.1703</v>
       </c>
       <c r="J20" t="n">
         <v>150846</v>
@@ -2484,7 +2484,7 @@
         <v>76221</v>
       </c>
       <c r="M20" t="n">
-        <v>31.75</v>
+        <v>31.7472</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>140741</v>
       </c>
       <c r="R20" t="n">
-        <v>85.89</v>
+        <v>85.8879</v>
       </c>
       <c r="S20" t="n">
         <v>66717</v>
@@ -2562,7 +2562,7 @@
         <v>1305</v>
       </c>
       <c r="I21" t="n">
-        <v>40.68</v>
+        <v>40.6844</v>
       </c>
       <c r="J21" t="n">
         <v>141393</v>
@@ -2574,7 +2574,7 @@
         <v>84466</v>
       </c>
       <c r="M21" t="n">
-        <v>35.43</v>
+        <v>35.4342</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>131824</v>
       </c>
       <c r="R21" t="n">
-        <v>85.65000000000001</v>
+        <v>85.6512</v>
       </c>
       <c r="S21" t="n">
         <v>74123</v>
@@ -2652,7 +2652,7 @@
         <v>639</v>
       </c>
       <c r="I22" t="n">
-        <v>42.18</v>
+        <v>42.1818</v>
       </c>
       <c r="J22" t="n">
         <v>162135</v>
@@ -2664,7 +2664,7 @@
         <v>99020</v>
       </c>
       <c r="M22" t="n">
-        <v>35.31</v>
+        <v>35.3111</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>163339</v>
       </c>
       <c r="R22" t="n">
-        <v>90.04000000000001</v>
+        <v>90.04259999999999</v>
       </c>
       <c r="S22" t="n">
         <v>98568</v>
@@ -2742,7 +2742,7 @@
         <v>1366</v>
       </c>
       <c r="I23" t="n">
-        <v>38.76</v>
+        <v>38.7568</v>
       </c>
       <c r="J23" t="n">
         <v>175123</v>
@@ -2754,7 +2754,7 @@
         <v>89411</v>
       </c>
       <c r="M23" t="n">
-        <v>31.27</v>
+        <v>31.2684</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>172831</v>
       </c>
       <c r="R23" t="n">
-        <v>87.94</v>
+        <v>87.93859999999999</v>
       </c>
       <c r="S23" t="n">
         <v>90396</v>
@@ -2832,7 +2832,7 @@
         <v>809</v>
       </c>
       <c r="I24" t="n">
-        <v>31.87</v>
+        <v>31.868</v>
       </c>
       <c r="J24" t="n">
         <v>186489</v>
@@ -2844,7 +2844,7 @@
         <v>73020</v>
       </c>
       <c r="M24" t="n">
-        <v>26.68</v>
+        <v>26.6772</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>160401</v>
       </c>
       <c r="R24" t="n">
-        <v>79.92</v>
+        <v>79.922</v>
       </c>
       <c r="S24" t="n">
         <v>60143</v>
@@ -2922,7 +2922,7 @@
         <v>908</v>
       </c>
       <c r="I25" t="n">
-        <v>40.76</v>
+        <v>40.7644</v>
       </c>
       <c r="J25" t="n">
         <v>139498</v>
@@ -2934,7 +2934,7 @@
         <v>80554</v>
       </c>
       <c r="M25" t="n">
-        <v>34.21</v>
+        <v>34.206</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>133928</v>
       </c>
       <c r="R25" t="n">
-        <v>86.44</v>
+        <v>86.43689999999999</v>
       </c>
       <c r="S25" t="n">
         <v>74900</v>
@@ -3012,7 +3012,7 @@
         <v>259</v>
       </c>
       <c r="I26" t="n">
-        <v>32.56</v>
+        <v>32.5589</v>
       </c>
       <c r="J26" t="n">
         <v>181592</v>
@@ -3024,7 +3024,7 @@
         <v>74529</v>
       </c>
       <c r="M26" t="n">
-        <v>27.68</v>
+        <v>27.6792</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>150594</v>
       </c>
       <c r="R26" t="n">
-        <v>77.33</v>
+        <v>77.3344</v>
       </c>
       <c r="S26" t="n">
         <v>63985</v>
@@ -3102,7 +3102,7 @@
         <v>1503</v>
       </c>
       <c r="I27" t="n">
-        <v>40.16</v>
+        <v>40.1616</v>
       </c>
       <c r="J27" t="n">
         <v>189999</v>
@@ -3114,7 +3114,7 @@
         <v>105829</v>
       </c>
       <c r="M27" t="n">
-        <v>33.33</v>
+        <v>33.3299</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>184815</v>
       </c>
       <c r="R27" t="n">
-        <v>87.3</v>
+        <v>87.30410000000001</v>
       </c>
       <c r="S27" t="n">
         <v>99607</v>
@@ -3192,7 +3192,7 @@
         <v>4846</v>
       </c>
       <c r="I28" t="n">
-        <v>31.1</v>
+        <v>31.0967</v>
       </c>
       <c r="J28" t="n">
         <v>484011</v>
@@ -3204,7 +3204,7 @@
         <v>165459</v>
       </c>
       <c r="M28" t="n">
-        <v>23.55</v>
+        <v>23.5546</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>447295</v>
       </c>
       <c r="R28" t="n">
-        <v>83.3</v>
+        <v>83.2966</v>
       </c>
       <c r="S28" t="n">
         <v>163009</v>
@@ -3282,7 +3282,7 @@
         <v>3198</v>
       </c>
       <c r="I29" t="n">
-        <v>33.07</v>
+        <v>33.0701</v>
       </c>
       <c r="J29" t="n">
         <v>267271</v>
@@ -3294,7 +3294,7 @@
         <v>103278</v>
       </c>
       <c r="M29" t="n">
-        <v>25.86</v>
+        <v>25.8628</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>261570</v>
       </c>
       <c r="R29" t="n">
-        <v>88.34999999999999</v>
+        <v>88.3527</v>
       </c>
       <c r="S29" t="n">
         <v>104270</v>
@@ -3372,7 +3372,7 @@
         <v>2768</v>
       </c>
       <c r="I30" t="n">
-        <v>13.34</v>
+        <v>13.3447</v>
       </c>
       <c r="J30" t="n">
         <v>355316</v>
@@ -3384,7 +3384,7 @@
         <v>34113</v>
       </c>
       <c r="M30" t="n">
-        <v>8.32</v>
+        <v>8.319599999999999</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>331088</v>
       </c>
       <c r="R30" t="n">
-        <v>88.06999999999999</v>
+        <v>88.07380000000001</v>
       </c>
       <c r="S30" t="n">
         <v>35101</v>
@@ -3462,7 +3462,7 @@
         <v>4947</v>
       </c>
       <c r="I31" t="n">
-        <v>33.7</v>
+        <v>33.6978</v>
       </c>
       <c r="J31" t="n">
         <v>294712</v>
@@ -3474,7 +3474,7 @@
         <v>114281</v>
       </c>
       <c r="M31" t="n">
-        <v>25.71</v>
+        <v>25.7101</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>283677</v>
       </c>
       <c r="R31" t="n">
-        <v>85.91</v>
+        <v>85.9062</v>
       </c>
       <c r="S31" t="n">
         <v>108152</v>
@@ -3552,7 +3552,7 @@
         <v>3652</v>
       </c>
       <c r="I32" t="n">
-        <v>29.15</v>
+        <v>29.1535</v>
       </c>
       <c r="J32" t="n">
         <v>294355</v>
@@ -3564,7 +3564,7 @@
         <v>91806</v>
       </c>
       <c r="M32" t="n">
-        <v>22.1</v>
+        <v>22.0962</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>278809</v>
       </c>
       <c r="R32" t="n">
-        <v>86.14</v>
+        <v>86.13800000000001</v>
       </c>
       <c r="S32" t="n">
         <v>89513</v>
@@ -3642,7 +3642,7 @@
         <v>5174</v>
       </c>
       <c r="I33" t="n">
-        <v>23.85</v>
+        <v>23.8536</v>
       </c>
       <c r="J33" t="n">
         <v>339232</v>
@@ -3654,7 +3654,7 @@
         <v>79100</v>
       </c>
       <c r="M33" t="n">
-        <v>17.76</v>
+        <v>17.7553</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>324010</v>
       </c>
       <c r="R33" t="n">
-        <v>88.43000000000001</v>
+        <v>88.4307</v>
       </c>
       <c r="S33" t="n">
         <v>76424</v>
@@ -3732,7 +3732,7 @@
         <v>2052</v>
       </c>
       <c r="I34" t="n">
-        <v>14.88</v>
+        <v>14.8835</v>
       </c>
       <c r="J34" t="n">
         <v>271976</v>
@@ -3744,7 +3744,7 @@
         <v>30133</v>
       </c>
       <c r="M34" t="n">
-        <v>9.43</v>
+        <v>9.430300000000001</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>262409</v>
       </c>
       <c r="R34" t="n">
-        <v>90.67</v>
+        <v>90.67310000000001</v>
       </c>
       <c r="S34" t="n">
         <v>33841</v>
@@ -3822,7 +3822,7 @@
         <v>1901</v>
       </c>
       <c r="I35" t="n">
-        <v>14.19</v>
+        <v>14.192</v>
       </c>
       <c r="J35" t="n">
         <v>195861</v>
@@ -3834,7 +3834,7 @@
         <v>26200</v>
       </c>
       <c r="M35" t="n">
-        <v>11.48</v>
+        <v>11.4784</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>187584</v>
       </c>
       <c r="R35" t="n">
-        <v>92.84</v>
+        <v>92.8381</v>
       </c>
       <c r="S35" t="n">
         <v>22449</v>
@@ -3912,7 +3912,7 @@
         <v>1164</v>
       </c>
       <c r="I36" t="n">
-        <v>11.35</v>
+        <v>11.3529</v>
       </c>
       <c r="J36" t="n">
         <v>205344</v>
@@ -3924,7 +3924,7 @@
         <v>20347</v>
       </c>
       <c r="M36" t="n">
-        <v>8.779999999999999</v>
+        <v>8.783799999999999</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>198251</v>
       </c>
       <c r="R36" t="n">
-        <v>93.83</v>
+        <v>93.8266</v>
       </c>
       <c r="S36" t="n">
         <v>16768</v>
@@ -4002,7 +4002,7 @@
         <v>2012</v>
       </c>
       <c r="I37" t="n">
-        <v>13.66</v>
+        <v>13.6647</v>
       </c>
       <c r="J37" t="n">
         <v>237024</v>
@@ -4014,7 +4014,7 @@
         <v>30617</v>
       </c>
       <c r="M37" t="n">
-        <v>11.15</v>
+        <v>11.1521</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>227765</v>
       </c>
       <c r="R37" t="n">
-        <v>93.38</v>
+        <v>93.3762</v>
       </c>
       <c r="S37" t="n">
         <v>22961</v>
@@ -4092,7 +4092,7 @@
         <v>2741</v>
       </c>
       <c r="I38" t="n">
-        <v>15.75</v>
+        <v>15.7525</v>
       </c>
       <c r="J38" t="n">
         <v>267313</v>
@@ -4104,7 +4104,7 @@
         <v>40996</v>
       </c>
       <c r="M38" t="n">
-        <v>12.92</v>
+        <v>12.9205</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>246317</v>
       </c>
       <c r="R38" t="n">
-        <v>89.15000000000001</v>
+        <v>89.14870000000001</v>
       </c>
       <c r="S38" t="n">
         <v>30450</v>
@@ -4182,7 +4182,7 @@
         <v>1723</v>
       </c>
       <c r="I39" t="n">
-        <v>18.15</v>
+        <v>18.1468</v>
       </c>
       <c r="J39" t="n">
         <v>191800</v>
@@ -4194,7 +4194,7 @@
         <v>35157</v>
       </c>
       <c r="M39" t="n">
-        <v>15</v>
+        <v>15.0037</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>182340</v>
       </c>
       <c r="R39" t="n">
-        <v>91.55</v>
+        <v>91.5522</v>
       </c>
       <c r="S39" t="n">
         <v>28345</v>
@@ -4272,7 +4272,7 @@
         <v>2000</v>
       </c>
       <c r="I40" t="n">
-        <v>12.68</v>
+        <v>12.6824</v>
       </c>
       <c r="J40" t="n">
         <v>248967</v>
@@ -4284,7 +4284,7 @@
         <v>29010</v>
       </c>
       <c r="M40" t="n">
-        <v>10.17</v>
+        <v>10.1744</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>233684</v>
       </c>
       <c r="R40" t="n">
-        <v>91.23999999999999</v>
+        <v>91.24079999999999</v>
       </c>
       <c r="S40" t="n">
         <v>21417</v>
@@ -4362,7 +4362,7 @@
         <v>1227</v>
       </c>
       <c r="I41" t="n">
-        <v>14.19</v>
+        <v>14.186</v>
       </c>
       <c r="J41" t="n">
         <v>215751</v>
@@ -4374,7 +4374,7 @@
         <v>25608</v>
       </c>
       <c r="M41" t="n">
-        <v>10.19</v>
+        <v>10.1855</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>203497</v>
       </c>
       <c r="R41" t="n">
-        <v>90.12</v>
+        <v>90.1191</v>
       </c>
       <c r="S41" t="n">
         <v>25515</v>
@@ -4452,7 +4452,7 @@
         <v>1984</v>
       </c>
       <c r="I42" t="n">
-        <v>13.55</v>
+        <v>13.5491</v>
       </c>
       <c r="J42" t="n">
         <v>235960</v>
@@ -4464,7 +4464,7 @@
         <v>27088</v>
       </c>
       <c r="M42" t="n">
-        <v>9.92</v>
+        <v>9.9245</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>221038</v>
       </c>
       <c r="R42" t="n">
-        <v>89.91</v>
+        <v>89.9066</v>
       </c>
       <c r="S42" t="n">
         <v>23286</v>
@@ -4542,7 +4542,7 @@
         <v>1168</v>
       </c>
       <c r="I43" t="n">
-        <v>11.12</v>
+        <v>11.1165</v>
       </c>
       <c r="J43" t="n">
         <v>235816</v>
@@ -4554,7 +4554,7 @@
         <v>21744</v>
       </c>
       <c r="M43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1957</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>225786</v>
       </c>
       <c r="R43" t="n">
-        <v>92.7</v>
+        <v>92.70050000000001</v>
       </c>
       <c r="S43" t="n">
         <v>17000</v>
@@ -4632,7 +4632,7 @@
         <v>968</v>
       </c>
       <c r="I44" t="n">
-        <v>21.54</v>
+        <v>21.5428</v>
       </c>
       <c r="J44" t="n">
         <v>198722</v>
@@ -4644,7 +4644,7 @@
         <v>42224</v>
       </c>
       <c r="M44" t="n">
-        <v>16.67</v>
+        <v>16.6704</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>190527</v>
       </c>
       <c r="R44" t="n">
-        <v>90.27</v>
+        <v>90.2702</v>
       </c>
       <c r="S44" t="n">
         <v>42834</v>
@@ -4722,7 +4722,7 @@
         <v>2022</v>
       </c>
       <c r="I45" t="n">
-        <v>13.87</v>
+        <v>13.869</v>
       </c>
       <c r="J45" t="n">
         <v>227645</v>
@@ -4734,7 +4734,7 @@
         <v>29563</v>
       </c>
       <c r="M45" t="n">
-        <v>11.19</v>
+        <v>11.1854</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>216318</v>
       </c>
       <c r="R45" t="n">
-        <v>92.15000000000001</v>
+        <v>92.15300000000001</v>
       </c>
       <c r="S45" t="n">
         <v>23671</v>
@@ -4812,7 +4812,7 @@
         <v>1593</v>
       </c>
       <c r="I46" t="n">
-        <v>12.43</v>
+        <v>12.4316</v>
       </c>
       <c r="J46" t="n">
         <v>207382</v>
@@ -4824,7 +4824,7 @@
         <v>23372</v>
       </c>
       <c r="M46" t="n">
-        <v>9.869999999999999</v>
+        <v>9.869</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>189892</v>
       </c>
       <c r="R46" t="n">
-        <v>88.95999999999999</v>
+        <v>88.9628</v>
       </c>
       <c r="S46" t="n">
         <v>16014</v>
@@ -4902,7 +4902,7 @@
         <v>4245</v>
       </c>
       <c r="I47" t="n">
-        <v>19.75</v>
+        <v>19.7499</v>
       </c>
       <c r="J47" t="n">
         <v>238505</v>
@@ -4914,7 +4914,7 @@
         <v>48676</v>
       </c>
       <c r="M47" t="n">
-        <v>16.38</v>
+        <v>16.3781</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>229076</v>
       </c>
       <c r="R47" t="n">
-        <v>92.17</v>
+        <v>92.1739</v>
       </c>
       <c r="S47" t="n">
         <v>43570</v>
@@ -4992,7 +4992,7 @@
         <v>2751</v>
       </c>
       <c r="I48" t="n">
-        <v>11.81</v>
+        <v>11.8063</v>
       </c>
       <c r="J48" t="n">
         <v>232804</v>
@@ -5004,7 +5004,7 @@
         <v>23749</v>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>8.9969</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>212534</v>
       </c>
       <c r="R48" t="n">
-        <v>88.47</v>
+        <v>88.4747</v>
       </c>
       <c r="S48" t="n">
         <v>18858</v>
@@ -5082,7 +5082,7 @@
         <v>2509</v>
       </c>
       <c r="I49" t="n">
-        <v>16.29</v>
+        <v>16.2903</v>
       </c>
       <c r="J49" t="n">
         <v>206486</v>
@@ -5094,7 +5094,7 @@
         <v>34038</v>
       </c>
       <c r="M49" t="n">
-        <v>13.8</v>
+        <v>13.7991</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>195584</v>
       </c>
       <c r="R49" t="n">
-        <v>91.98</v>
+        <v>91.9828</v>
       </c>
       <c r="S49" t="n">
         <v>27494</v>
@@ -5172,7 +5172,7 @@
         <v>2225</v>
       </c>
       <c r="I50" t="n">
-        <v>8.26</v>
+        <v>8.2582</v>
       </c>
       <c r="J50" t="n">
         <v>226693</v>
@@ -5184,7 +5184,7 @@
         <v>13269</v>
       </c>
       <c r="M50" t="n">
-        <v>5.37</v>
+        <v>5.3699</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>213042</v>
       </c>
       <c r="R50" t="n">
-        <v>91.11</v>
+        <v>91.10980000000001</v>
       </c>
       <c r="S50" t="n">
         <v>12156</v>
@@ -5262,7 +5262,7 @@
         <v>1810</v>
       </c>
       <c r="I51" t="n">
-        <v>10.34</v>
+        <v>10.3383</v>
       </c>
       <c r="J51" t="n">
         <v>216689</v>
@@ -5274,7 +5274,7 @@
         <v>16756</v>
       </c>
       <c r="M51" t="n">
-        <v>6.93</v>
+        <v>6.9333</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>202925</v>
       </c>
       <c r="R51" t="n">
-        <v>90.22</v>
+        <v>90.2218</v>
       </c>
       <c r="S51" t="n">
         <v>15772</v>
@@ -5352,7 +5352,7 @@
         <v>1641</v>
       </c>
       <c r="I52" t="n">
-        <v>9.050000000000001</v>
+        <v>9.053900000000001</v>
       </c>
       <c r="J52" t="n">
         <v>228594</v>
@@ -5364,7 +5364,7 @@
         <v>17851</v>
       </c>
       <c r="M52" t="n">
-        <v>7.1</v>
+        <v>7.102</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>205530</v>
       </c>
       <c r="R52" t="n">
-        <v>88.02</v>
+        <v>88.0214</v>
       </c>
       <c r="S52" t="n">
         <v>10790</v>
@@ -5442,7 +5442,7 @@
         <v>1988</v>
       </c>
       <c r="I53" t="n">
-        <v>10.04</v>
+        <v>10.0435</v>
       </c>
       <c r="J53" t="n">
         <v>230617</v>
@@ -5454,7 +5454,7 @@
         <v>19016</v>
       </c>
       <c r="M53" t="n">
-        <v>7.42</v>
+        <v>7.4175</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>213960</v>
       </c>
       <c r="R53" t="n">
-        <v>90.15000000000001</v>
+        <v>90.14570000000001</v>
       </c>
       <c r="S53" t="n">
         <v>13631</v>
@@ -5532,7 +5532,7 @@
         <v>1106</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>8.997999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>257501</v>
@@ -5544,7 +5544,7 @@
         <v>17925</v>
       </c>
       <c r="M54" t="n">
-        <v>6.33</v>
+        <v>6.3348</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>230181</v>
       </c>
       <c r="R54" t="n">
-        <v>86.84999999999999</v>
+        <v>86.8486</v>
       </c>
       <c r="S54" t="n">
         <v>11790</v>
@@ -5622,7 +5622,7 @@
         <v>1638</v>
       </c>
       <c r="I55" t="n">
-        <v>10.78</v>
+        <v>10.7847</v>
       </c>
       <c r="J55" t="n">
         <v>236780</v>
@@ -5634,7 +5634,7 @@
         <v>21528</v>
       </c>
       <c r="M55" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1114</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>222608</v>
       </c>
       <c r="R55" t="n">
-        <v>91.28</v>
+        <v>91.2795</v>
       </c>
       <c r="S55" t="n">
         <v>13530</v>
@@ -5712,7 +5712,7 @@
         <v>2136</v>
       </c>
       <c r="I56" t="n">
-        <v>11.85</v>
+        <v>11.8463</v>
       </c>
       <c r="J56" t="n">
         <v>324791</v>
@@ -5724,7 +5724,7 @@
         <v>30142</v>
       </c>
       <c r="M56" t="n">
-        <v>8.18</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>277770</v>
       </c>
       <c r="R56" t="n">
-        <v>82.11</v>
+        <v>82.1088</v>
       </c>
       <c r="S56" t="n">
         <v>25746</v>
@@ -5802,7 +5802,7 @@
         <v>2143</v>
       </c>
       <c r="I57" t="n">
-        <v>11.06</v>
+        <v>11.0555</v>
       </c>
       <c r="J57" t="n">
         <v>227794</v>
@@ -5814,7 +5814,7 @@
         <v>20124</v>
       </c>
       <c r="M57" t="n">
-        <v>7.86</v>
+        <v>7.8576</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>205878</v>
       </c>
       <c r="R57" t="n">
-        <v>87.23999999999999</v>
+        <v>87.2424</v>
       </c>
       <c r="S57" t="n">
         <v>13497</v>
@@ -5892,7 +5892,7 @@
         <v>1125</v>
       </c>
       <c r="I58" t="n">
-        <v>6.02</v>
+        <v>6.0181</v>
       </c>
       <c r="J58" t="n">
         <v>230797</v>
@@ -5904,7 +5904,7 @@
         <v>8100</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>3.2984</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>225257</v>
       </c>
       <c r="R58" t="n">
-        <v>94.84999999999999</v>
+        <v>94.8546</v>
       </c>
       <c r="S58" t="n">
         <v>9583</v>
@@ -5982,7 +5982,7 @@
         <v>998</v>
       </c>
       <c r="I59" t="n">
-        <v>5.63</v>
+        <v>5.6338</v>
       </c>
       <c r="J59" t="n">
         <v>239492</v>
@@ -5994,7 +5994,7 @@
         <v>7497</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>2.954</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>228666</v>
       </c>
       <c r="R59" t="n">
-        <v>92.84</v>
+        <v>92.84310000000001</v>
       </c>
       <c r="S59" t="n">
         <v>9824</v>
@@ -6072,7 +6072,7 @@
         <v>1340</v>
       </c>
       <c r="I60" t="n">
-        <v>8.09</v>
+        <v>8.091100000000001</v>
       </c>
       <c r="J60" t="n">
         <v>248802</v>
@@ -6084,7 +6084,7 @@
         <v>12766</v>
       </c>
       <c r="M60" t="n">
-        <v>4.72</v>
+        <v>4.7158</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>238579</v>
       </c>
       <c r="R60" t="n">
-        <v>92.48999999999999</v>
+        <v>92.4943</v>
       </c>
       <c r="S60" t="n">
         <v>14826</v>
@@ -6162,7 +6162,7 @@
         <v>1715</v>
       </c>
       <c r="I61" t="n">
-        <v>5.9</v>
+        <v>5.8972</v>
       </c>
       <c r="J61" t="n">
         <v>247577</v>
@@ -6174,7 +6174,7 @@
         <v>8434</v>
       </c>
       <c r="M61" t="n">
-        <v>3.21</v>
+        <v>3.2057</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>236621</v>
       </c>
       <c r="R61" t="n">
-        <v>92.92</v>
+        <v>92.91719999999999</v>
       </c>
       <c r="S61" t="n">
         <v>10357</v>
@@ -6252,7 +6252,7 @@
         <v>1725</v>
       </c>
       <c r="I62" t="n">
-        <v>5.95</v>
+        <v>5.954</v>
       </c>
       <c r="J62" t="n">
         <v>237249</v>
@@ -6264,7 +6264,7 @@
         <v>8527</v>
       </c>
       <c r="M62" t="n">
-        <v>3.38</v>
+        <v>3.3801</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>220042</v>
       </c>
       <c r="R62" t="n">
-        <v>90.28</v>
+        <v>90.2766</v>
       </c>
       <c r="S62" t="n">
         <v>8293</v>
@@ -6342,7 +6342,7 @@
         <v>1858</v>
       </c>
       <c r="I63" t="n">
-        <v>9.67</v>
+        <v>9.672800000000001</v>
       </c>
       <c r="J63" t="n">
         <v>259604</v>
@@ -6354,7 +6354,7 @@
         <v>20775</v>
       </c>
       <c r="M63" t="n">
-        <v>7.23</v>
+        <v>7.2285</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>242897</v>
       </c>
       <c r="R63" t="n">
-        <v>91.09999999999999</v>
+        <v>91.0992</v>
       </c>
       <c r="S63" t="n">
         <v>15028</v>
@@ -6432,7 +6432,7 @@
         <v>1611</v>
       </c>
       <c r="I64" t="n">
-        <v>15.01</v>
+        <v>15.0111</v>
       </c>
       <c r="J64" t="n">
         <v>238970</v>
@@ -6444,7 +6444,7 @@
         <v>33869</v>
       </c>
       <c r="M64" t="n">
-        <v>12.05</v>
+        <v>12.0454</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>220066</v>
       </c>
       <c r="R64" t="n">
-        <v>88.98</v>
+        <v>88.9842</v>
       </c>
       <c r="S64" t="n">
         <v>28197</v>
@@ -6522,7 +6522,7 @@
         <v>1030</v>
       </c>
       <c r="I65" t="n">
-        <v>10.37</v>
+        <v>10.367</v>
       </c>
       <c r="J65" t="n">
         <v>233529</v>
@@ -6534,7 +6534,7 @@
         <v>21626</v>
       </c>
       <c r="M65" t="n">
-        <v>8.300000000000001</v>
+        <v>8.3005</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>219790</v>
       </c>
       <c r="R65" t="n">
-        <v>92</v>
+        <v>91.9958</v>
       </c>
       <c r="S65" t="n">
         <v>15698</v>
@@ -6612,7 +6612,7 @@
         <v>1340</v>
       </c>
       <c r="I66" t="n">
-        <v>9.51</v>
+        <v>9.5113</v>
       </c>
       <c r="J66" t="n">
         <v>225039</v>
@@ -6624,7 +6624,7 @@
         <v>17927</v>
       </c>
       <c r="M66" t="n">
-        <v>7.21</v>
+        <v>7.2085</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>214127</v>
       </c>
       <c r="R66" t="n">
-        <v>92.79000000000001</v>
+        <v>92.7897</v>
       </c>
       <c r="S66" t="n">
         <v>13281</v>
@@ -6702,7 +6702,7 @@
         <v>992</v>
       </c>
       <c r="I67" t="n">
-        <v>8.01</v>
+        <v>8.0124</v>
       </c>
       <c r="J67" t="n">
         <v>227178</v>
@@ -6714,7 +6714,7 @@
         <v>14540</v>
       </c>
       <c r="M67" t="n">
-        <v>5.89</v>
+        <v>5.8875</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>211743</v>
       </c>
       <c r="R67" t="n">
-        <v>91.09999999999999</v>
+        <v>91.10129999999999</v>
       </c>
       <c r="S67" t="n">
         <v>10918</v>
@@ -6792,7 +6792,7 @@
         <v>1780</v>
       </c>
       <c r="I68" t="n">
-        <v>13.04</v>
+        <v>13.0385</v>
       </c>
       <c r="J68" t="n">
         <v>246208</v>
@@ -6804,7 +6804,7 @@
         <v>30101</v>
       </c>
       <c r="M68" t="n">
-        <v>10.63</v>
+        <v>10.6318</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>230162</v>
       </c>
       <c r="R68" t="n">
-        <v>90.97</v>
+        <v>90.9652</v>
       </c>
       <c r="S68" t="n">
         <v>18543</v>
@@ -6882,7 +6882,7 @@
         <v>770</v>
       </c>
       <c r="I69" t="n">
-        <v>12.41</v>
+        <v>12.4118</v>
       </c>
       <c r="J69" t="n">
         <v>232720</v>
@@ -6894,7 +6894,7 @@
         <v>27415</v>
       </c>
       <c r="M69" t="n">
-        <v>10.32</v>
+        <v>10.3181</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>222570</v>
       </c>
       <c r="R69" t="n">
-        <v>93.41</v>
+        <v>93.4057</v>
       </c>
       <c r="S69" t="n">
         <v>18320</v>
@@ -6972,7 +6972,7 @@
         <v>1146</v>
       </c>
       <c r="I70" t="n">
-        <v>16.84</v>
+        <v>16.838</v>
       </c>
       <c r="J70" t="n">
         <v>206492</v>
@@ -6984,7 +6984,7 @@
         <v>36490</v>
       </c>
       <c r="M70" t="n">
-        <v>14.7</v>
+        <v>14.6959</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>191204</v>
       </c>
       <c r="R70" t="n">
-        <v>90.27</v>
+        <v>90.271</v>
       </c>
       <c r="S70" t="n">
         <v>22450</v>
@@ -7062,7 +7062,7 @@
         <v>1153</v>
       </c>
       <c r="I71" t="n">
-        <v>9.859999999999999</v>
+        <v>9.861800000000001</v>
       </c>
       <c r="J71" t="n">
         <v>234920</v>
@@ -7074,7 +7074,7 @@
         <v>19665</v>
       </c>
       <c r="M71" t="n">
-        <v>7.55</v>
+        <v>7.5454</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>216652</v>
       </c>
       <c r="R71" t="n">
-        <v>89.91</v>
+        <v>89.9131</v>
       </c>
       <c r="S71" t="n">
         <v>15020</v>
@@ -7152,7 +7152,7 @@
         <v>689</v>
       </c>
       <c r="I72" t="n">
-        <v>7.75</v>
+        <v>7.7544</v>
       </c>
       <c r="J72" t="n">
         <v>202528</v>
@@ -7164,7 +7164,7 @@
         <v>11888</v>
       </c>
       <c r="M72" t="n">
-        <v>5.41</v>
+        <v>5.4146</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>189221</v>
       </c>
       <c r="R72" t="n">
-        <v>91.12</v>
+        <v>91.11839999999999</v>
       </c>
       <c r="S72" t="n">
         <v>8397</v>
@@ -7242,7 +7242,7 @@
         <v>962</v>
       </c>
       <c r="I73" t="n">
-        <v>10.23</v>
+        <v>10.2345</v>
       </c>
       <c r="J73" t="n">
         <v>212097</v>
@@ -7254,7 +7254,7 @@
         <v>18670</v>
       </c>
       <c r="M73" t="n">
-        <v>7.9</v>
+        <v>7.9017</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>196026</v>
       </c>
       <c r="R73" t="n">
-        <v>90.08</v>
+        <v>90.0818</v>
       </c>
       <c r="S73" t="n">
         <v>12829</v>
@@ -7332,7 +7332,7 @@
         <v>1122</v>
       </c>
       <c r="I74" t="n">
-        <v>13.37</v>
+        <v>13.3669</v>
       </c>
       <c r="J74" t="n">
         <v>203683</v>
@@ -7344,7 +7344,7 @@
         <v>27126</v>
       </c>
       <c r="M74" t="n">
-        <v>11.54</v>
+        <v>11.5376</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>192119</v>
       </c>
       <c r="R74" t="n">
-        <v>92.37</v>
+        <v>92.372</v>
       </c>
       <c r="S74" t="n">
         <v>19630</v>
@@ -7422,7 +7422,7 @@
         <v>1194</v>
       </c>
       <c r="I75" t="n">
-        <v>11.73</v>
+        <v>11.7285</v>
       </c>
       <c r="J75" t="n">
         <v>235083</v>
@@ -7434,7 +7434,7 @@
         <v>22238</v>
       </c>
       <c r="M75" t="n">
-        <v>8.35</v>
+        <v>8.350199999999999</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>215422</v>
       </c>
       <c r="R75" t="n">
-        <v>88.26000000000001</v>
+        <v>88.25879999999999</v>
       </c>
       <c r="S75" t="n">
         <v>18751</v>
@@ -7512,7 +7512,7 @@
         <v>1517</v>
       </c>
       <c r="I76" t="n">
-        <v>8.960000000000001</v>
+        <v>8.9558</v>
       </c>
       <c r="J76" t="n">
         <v>222796</v>
@@ -7524,7 +7524,7 @@
         <v>17357</v>
       </c>
       <c r="M76" t="n">
-        <v>7.09</v>
+        <v>7.0928</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>209231</v>
       </c>
       <c r="R76" t="n">
-        <v>92.03</v>
+        <v>92.0283</v>
       </c>
       <c r="S76" t="n">
         <v>11933</v>
@@ -7602,7 +7602,7 @@
         <v>1361</v>
       </c>
       <c r="I77" t="n">
-        <v>11.85</v>
+        <v>11.8454</v>
       </c>
       <c r="J77" t="n">
         <v>233518</v>
@@ -7614,7 +7614,7 @@
         <v>23893</v>
       </c>
       <c r="M77" t="n">
-        <v>9.02</v>
+        <v>9.0198</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>217318</v>
       </c>
       <c r="R77" t="n">
-        <v>90.17</v>
+        <v>90.17230000000001</v>
       </c>
       <c r="S77" t="n">
         <v>18087</v>
@@ -7692,7 +7692,7 @@
         <v>1317</v>
       </c>
       <c r="I78" t="n">
-        <v>5.73</v>
+        <v>5.7313</v>
       </c>
       <c r="J78" t="n">
         <v>287413</v>
@@ -7704,7 +7704,7 @@
         <v>7415</v>
       </c>
       <c r="M78" t="n">
-        <v>2.43</v>
+        <v>2.432</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>271002</v>
       </c>
       <c r="R78" t="n">
-        <v>91.09999999999999</v>
+        <v>91.10169999999999</v>
       </c>
       <c r="S78" t="n">
         <v>8215</v>
@@ -7782,7 +7782,7 @@
         <v>1643</v>
       </c>
       <c r="I79" t="n">
-        <v>7.18</v>
+        <v>7.1822</v>
       </c>
       <c r="J79" t="n">
         <v>262564</v>
@@ -7794,7 +7794,7 @@
         <v>12340</v>
       </c>
       <c r="M79" t="n">
-        <v>4.36</v>
+        <v>4.3623</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>244795</v>
       </c>
       <c r="R79" t="n">
-        <v>90.48</v>
+        <v>90.48350000000001</v>
       </c>
       <c r="S79" t="n">
         <v>10557</v>
@@ -7872,7 +7872,7 @@
         <v>1483</v>
       </c>
       <c r="I80" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6366</v>
       </c>
       <c r="J80" t="n">
         <v>256161</v>
@@ -7884,7 +7884,7 @@
         <v>17240</v>
       </c>
       <c r="M80" t="n">
-        <v>6.15</v>
+        <v>6.1489</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>235528</v>
       </c>
       <c r="R80" t="n">
-        <v>89.51000000000001</v>
+        <v>89.5081</v>
       </c>
       <c r="S80" t="n">
         <v>13283</v>
@@ -7962,7 +7962,7 @@
         <v>1266</v>
       </c>
       <c r="I81" t="n">
-        <v>7.63</v>
+        <v>7.6328</v>
       </c>
       <c r="J81" t="n">
         <v>270140</v>
@@ -7974,7 +7974,7 @@
         <v>13701</v>
       </c>
       <c r="M81" t="n">
-        <v>4.68</v>
+        <v>4.6847</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>249626</v>
       </c>
       <c r="R81" t="n">
-        <v>89.55</v>
+        <v>89.54810000000001</v>
       </c>
       <c r="S81" t="n">
         <v>13439</v>
@@ -8052,7 +8052,7 @@
         <v>1756</v>
       </c>
       <c r="I82" t="n">
-        <v>9.640000000000001</v>
+        <v>9.6394</v>
       </c>
       <c r="J82" t="n">
         <v>211583</v>
@@ -8064,7 +8064,7 @@
         <v>17360</v>
       </c>
       <c r="M82" t="n">
-        <v>7.41</v>
+        <v>7.4139</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>196679</v>
       </c>
       <c r="R82" t="n">
-        <v>90.72</v>
+        <v>90.7216</v>
       </c>
       <c r="S82" t="n">
         <v>11759</v>
@@ -8142,7 +8142,7 @@
         <v>1541</v>
       </c>
       <c r="I83" t="n">
-        <v>10.21</v>
+        <v>10.2123</v>
       </c>
       <c r="J83" t="n">
         <v>220568</v>
@@ -8154,7 +8154,7 @@
         <v>19174</v>
       </c>
       <c r="M83" t="n">
-        <v>7.81</v>
+        <v>7.8053</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>208296</v>
       </c>
       <c r="R83" t="n">
-        <v>91.97</v>
+        <v>91.9706</v>
       </c>
       <c r="S83" t="n">
         <v>15128</v>
@@ -8232,7 +8232,7 @@
         <v>1708</v>
       </c>
       <c r="I84" t="n">
-        <v>8.32</v>
+        <v>8.315200000000001</v>
       </c>
       <c r="J84" t="n">
         <v>263724</v>
@@ -8244,7 +8244,7 @@
         <v>17113</v>
       </c>
       <c r="M84" t="n">
-        <v>5.95</v>
+        <v>5.9494</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>253592</v>
       </c>
       <c r="R84" t="n">
-        <v>93.73999999999999</v>
+        <v>93.7393</v>
       </c>
       <c r="S84" t="n">
         <v>14142</v>
@@ -8322,7 +8322,7 @@
         <v>1748</v>
       </c>
       <c r="I85" t="n">
-        <v>6.83</v>
+        <v>6.8262</v>
       </c>
       <c r="J85" t="n">
         <v>285233</v>
@@ -8334,7 +8334,7 @@
         <v>14264</v>
       </c>
       <c r="M85" t="n">
-        <v>4.66</v>
+        <v>4.6595</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>271119</v>
       </c>
       <c r="R85" t="n">
-        <v>92.89</v>
+        <v>92.8916</v>
       </c>
       <c r="S85" t="n">
         <v>11400</v>
@@ -8412,7 +8412,7 @@
         <v>2684</v>
       </c>
       <c r="I86" t="n">
-        <v>12.95</v>
+        <v>12.949</v>
       </c>
       <c r="J86" t="n">
         <v>245596</v>
@@ -8424,7 +8424,7 @@
         <v>28684</v>
       </c>
       <c r="M86" t="n">
-        <v>10.17</v>
+        <v>10.167</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>231105</v>
       </c>
       <c r="R86" t="n">
-        <v>91.19</v>
+        <v>91.1855</v>
       </c>
       <c r="S86" t="n">
         <v>24630</v>
@@ -8502,7 +8502,7 @@
         <v>2102</v>
       </c>
       <c r="I87" t="n">
-        <v>8.98</v>
+        <v>8.9788</v>
       </c>
       <c r="J87" t="n">
         <v>267374</v>
@@ -8514,7 +8514,7 @@
         <v>19695</v>
       </c>
       <c r="M87" t="n">
-        <v>6.7</v>
+        <v>6.7047</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>258263</v>
       </c>
       <c r="R87" t="n">
-        <v>94.23999999999999</v>
+        <v>94.238</v>
       </c>
       <c r="S87" t="n">
         <v>16069</v>
@@ -8592,7 +8592,7 @@
         <v>1426</v>
       </c>
       <c r="I88" t="n">
-        <v>8.710000000000001</v>
+        <v>8.711499999999999</v>
       </c>
       <c r="J88" t="n">
         <v>251866</v>
@@ -8604,7 +8604,7 @@
         <v>17223</v>
       </c>
       <c r="M88" t="n">
-        <v>6.24</v>
+        <v>6.2425</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>243779</v>
       </c>
       <c r="R88" t="n">
-        <v>94.23999999999999</v>
+        <v>94.2403</v>
       </c>
       <c r="S88" t="n">
         <v>14571</v>
@@ -8682,7 +8682,7 @@
         <v>2915</v>
       </c>
       <c r="I89" t="n">
-        <v>21.03</v>
+        <v>21.0271</v>
       </c>
       <c r="J89" t="n">
         <v>243941</v>
@@ -8694,7 +8694,7 @@
         <v>53572</v>
       </c>
       <c r="M89" t="n">
-        <v>17.34</v>
+        <v>17.3433</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>234407</v>
       </c>
       <c r="R89" t="n">
-        <v>91.81</v>
+        <v>91.8091</v>
       </c>
       <c r="S89" t="n">
         <v>47223</v>
@@ -8772,7 +8772,7 @@
         <v>1861</v>
       </c>
       <c r="I90" t="n">
-        <v>18.09</v>
+        <v>18.0851</v>
       </c>
       <c r="J90" t="n">
         <v>224423</v>
@@ -8784,7 +8784,7 @@
         <v>37883</v>
       </c>
       <c r="M90" t="n">
-        <v>13.83</v>
+        <v>13.8274</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>210712</v>
       </c>
       <c r="R90" t="n">
-        <v>89.25</v>
+        <v>89.25149999999999</v>
       </c>
       <c r="S90" t="n">
         <v>35735</v>
@@ -8862,7 +8862,7 @@
         <v>1052</v>
       </c>
       <c r="I91" t="n">
-        <v>16.72</v>
+        <v>16.7228</v>
       </c>
       <c r="J91" t="n">
         <v>213328</v>
@@ -8874,7 +8874,7 @@
         <v>32069</v>
       </c>
       <c r="M91" t="n">
-        <v>12.52</v>
+        <v>12.5188</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>207902</v>
       </c>
       <c r="R91" t="n">
-        <v>92.77</v>
+        <v>92.7732</v>
       </c>
       <c r="S91" t="n">
         <v>34044</v>
@@ -8952,7 +8952,7 @@
         <v>1378</v>
       </c>
       <c r="I92" t="n">
-        <v>9.65</v>
+        <v>9.6473</v>
       </c>
       <c r="J92" t="n">
         <v>240472</v>
@@ -8964,7 +8964,7 @@
         <v>17670</v>
       </c>
       <c r="M92" t="n">
-        <v>6.64</v>
+        <v>6.6392</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>235875</v>
       </c>
       <c r="R92" t="n">
-        <v>94.93000000000001</v>
+        <v>94.92789999999999</v>
       </c>
       <c r="S92" t="n">
         <v>16129</v>
@@ -9042,7 +9042,7 @@
         <v>1330</v>
       </c>
       <c r="I93" t="n">
-        <v>8.91</v>
+        <v>8.9061</v>
       </c>
       <c r="J93" t="n">
         <v>214825</v>
@@ -9054,7 +9054,7 @@
         <v>15274</v>
       </c>
       <c r="M93" t="n">
-        <v>6.48</v>
+        <v>6.4768</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>204680</v>
       </c>
       <c r="R93" t="n">
-        <v>92.8</v>
+        <v>92.8027</v>
       </c>
       <c r="S93" t="n">
         <v>12838</v>
@@ -9132,7 +9132,7 @@
         <v>1955</v>
       </c>
       <c r="I94" t="n">
-        <v>11.36</v>
+        <v>11.3587</v>
       </c>
       <c r="J94" t="n">
         <v>221051</v>
@@ -9144,7 +9144,7 @@
         <v>22050</v>
       </c>
       <c r="M94" t="n">
-        <v>8.84</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>209687</v>
       </c>
       <c r="R94" t="n">
-        <v>92.23999999999999</v>
+        <v>92.2403</v>
       </c>
       <c r="S94" t="n">
         <v>16090</v>
@@ -9222,7 +9222,7 @@
         <v>1549</v>
       </c>
       <c r="I95" t="n">
-        <v>13.68</v>
+        <v>13.6829</v>
       </c>
       <c r="J95" t="n">
         <v>227922</v>
@@ -9234,7 +9234,7 @@
         <v>28701</v>
       </c>
       <c r="M95" t="n">
-        <v>10.87</v>
+        <v>10.8694</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>212283</v>
       </c>
       <c r="R95" t="n">
-        <v>90.2</v>
+        <v>90.1985</v>
       </c>
       <c r="S95" t="n">
         <v>21729</v>
@@ -9312,7 +9312,7 @@
         <v>1220</v>
       </c>
       <c r="I96" t="n">
-        <v>10.68</v>
+        <v>10.6768</v>
       </c>
       <c r="J96" t="n">
         <v>198862</v>
@@ -9324,7 +9324,7 @@
         <v>19065</v>
       </c>
       <c r="M96" t="n">
-        <v>8.56</v>
+        <v>8.563499999999999</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>188845</v>
       </c>
       <c r="R96" t="n">
-        <v>92.77</v>
+        <v>92.768</v>
       </c>
       <c r="S96" t="n">
         <v>13472</v>
@@ -9402,7 +9402,7 @@
         <v>1040</v>
       </c>
       <c r="I97" t="n">
-        <v>13.7</v>
+        <v>13.7041</v>
       </c>
       <c r="J97" t="n">
         <v>200947</v>
@@ -9414,7 +9414,7 @@
         <v>25930</v>
       </c>
       <c r="M97" t="n">
-        <v>11.14</v>
+        <v>11.1355</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>191122</v>
       </c>
       <c r="R97" t="n">
-        <v>92.36</v>
+        <v>92.3616</v>
       </c>
       <c r="S97" t="n">
         <v>19297</v>
@@ -9504,7 +9504,7 @@
         <v>44689</v>
       </c>
       <c r="M98" t="n">
-        <v>17.06</v>
+        <v>17.0625</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>205324</v>
       </c>
       <c r="R98" t="n">
-        <v>94.52</v>
+        <v>94.5218</v>
       </c>
       <c r="S98" t="n">
         <v>34605</v>
@@ -9582,7 +9582,7 @@
         <v>1558</v>
       </c>
       <c r="I99" t="n">
-        <v>27.96</v>
+        <v>27.9627</v>
       </c>
       <c r="J99" t="n">
         <v>165510</v>
@@ -9594,7 +9594,7 @@
         <v>53528</v>
       </c>
       <c r="M99" t="n">
-        <v>23.3</v>
+        <v>23.2978</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>162453</v>
       </c>
       <c r="R99" t="n">
-        <v>92.18000000000001</v>
+        <v>92.18340000000001</v>
       </c>
       <c r="S99" t="n">
         <v>48461</v>
@@ -9672,7 +9672,7 @@
         <v>1872</v>
       </c>
       <c r="I100" t="n">
-        <v>24.17</v>
+        <v>24.1701</v>
       </c>
       <c r="J100" t="n">
         <v>230723</v>
@@ -9684,7 +9684,7 @@
         <v>58771</v>
       </c>
       <c r="M100" t="n">
-        <v>19.32</v>
+        <v>19.3158</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>221400</v>
       </c>
       <c r="R100" t="n">
-        <v>90.19</v>
+        <v>90.1859</v>
       </c>
       <c r="S100" t="n">
         <v>52706</v>
@@ -9762,7 +9762,7 @@
         <v>1465</v>
       </c>
       <c r="I101" t="n">
-        <v>13.56</v>
+        <v>13.5612</v>
       </c>
       <c r="J101" t="n">
         <v>198932</v>
@@ -9774,7 +9774,7 @@
         <v>24020</v>
       </c>
       <c r="M101" t="n">
-        <v>10.44</v>
+        <v>10.437</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>190759</v>
       </c>
       <c r="R101" t="n">
-        <v>92.55</v>
+        <v>92.5466</v>
       </c>
       <c r="S101" t="n">
         <v>20003</v>
@@ -9852,7 +9852,7 @@
         <v>2118</v>
       </c>
       <c r="I102" t="n">
-        <v>19.15</v>
+        <v>19.1521</v>
       </c>
       <c r="J102" t="n">
         <v>215158</v>
@@ -9864,7 +9864,7 @@
         <v>45384</v>
       </c>
       <c r="M102" t="n">
-        <v>17.05</v>
+        <v>17.0535</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>199944</v>
       </c>
       <c r="R102" t="n">
-        <v>90.58</v>
+        <v>90.57769999999999</v>
       </c>
       <c r="S102" t="n">
         <v>23767</v>
@@ -9942,7 +9942,7 @@
         <v>1664</v>
       </c>
       <c r="I103" t="n">
-        <v>21.45</v>
+        <v>21.4462</v>
       </c>
       <c r="J103" t="n">
         <v>210466</v>
@@ -9954,7 +9954,7 @@
         <v>51280</v>
       </c>
       <c r="M103" t="n">
-        <v>19.14</v>
+        <v>19.1396</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>203534</v>
       </c>
       <c r="R103" t="n">
-        <v>93.95</v>
+        <v>93.9477</v>
       </c>
       <c r="S103" t="n">
         <v>29108</v>
@@ -10032,7 +10032,7 @@
         <v>1440</v>
       </c>
       <c r="I104" t="n">
-        <v>14.63</v>
+        <v>14.6266</v>
       </c>
       <c r="J104" t="n">
         <v>204985</v>
@@ -10044,7 +10044,7 @@
         <v>28020</v>
       </c>
       <c r="M104" t="n">
-        <v>11.67</v>
+        <v>11.6699</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>200686</v>
       </c>
       <c r="R104" t="n">
-        <v>94.63</v>
+        <v>94.62569999999999</v>
       </c>
       <c r="S104" t="n">
         <v>19451</v>
@@ -10122,7 +10122,7 @@
         <v>1802</v>
       </c>
       <c r="I105" t="n">
-        <v>12.36</v>
+        <v>12.3575</v>
       </c>
       <c r="J105" t="n">
         <v>214272</v>
@@ -10134,7 +10134,7 @@
         <v>23091</v>
       </c>
       <c r="M105" t="n">
-        <v>9.44</v>
+        <v>9.444800000000001</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>208323</v>
       </c>
       <c r="R105" t="n">
-        <v>94.09999999999999</v>
+        <v>94.09650000000001</v>
       </c>
       <c r="S105" t="n">
         <v>18577</v>
@@ -10212,7 +10212,7 @@
         <v>1759</v>
       </c>
       <c r="I106" t="n">
-        <v>11.08</v>
+        <v>11.0799</v>
       </c>
       <c r="J106" t="n">
         <v>199285</v>
@@ -10224,7 +10224,7 @@
         <v>18380</v>
       </c>
       <c r="M106" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2011</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>185775</v>
       </c>
       <c r="R106" t="n">
-        <v>90.3</v>
+        <v>90.29730000000001</v>
       </c>
       <c r="S106" t="n">
         <v>11738</v>
@@ -10302,7 +10302,7 @@
         <v>1102</v>
       </c>
       <c r="I107" t="n">
-        <v>10.31</v>
+        <v>10.3066</v>
       </c>
       <c r="J107" t="n">
         <v>231164</v>
@@ -10314,7 +10314,7 @@
         <v>20146</v>
       </c>
       <c r="M107" t="n">
-        <v>7.82</v>
+        <v>7.8168</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>219727</v>
       </c>
       <c r="R107" t="n">
-        <v>92.48999999999999</v>
+        <v>92.4851</v>
       </c>
       <c r="S107" t="n">
         <v>14845</v>
@@ -10392,7 +10392,7 @@
         <v>2183</v>
       </c>
       <c r="I108" t="n">
-        <v>14.89</v>
+        <v>14.8938</v>
       </c>
       <c r="J108" t="n">
         <v>226889</v>
@@ -10404,7 +10404,7 @@
         <v>31011</v>
       </c>
       <c r="M108" t="n">
-        <v>11.63</v>
+        <v>11.6323</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>214595</v>
       </c>
       <c r="R108" t="n">
-        <v>91.09</v>
+        <v>91.0907</v>
       </c>
       <c r="S108" t="n">
         <v>23231</v>
@@ -10482,7 +10482,7 @@
         <v>1242</v>
       </c>
       <c r="I109" t="n">
-        <v>8.73</v>
+        <v>8.733599999999999</v>
       </c>
       <c r="J109" t="n">
         <v>182624</v>
@@ -10494,7 +10494,7 @@
         <v>12675</v>
       </c>
       <c r="M109" t="n">
-        <v>6.33</v>
+        <v>6.3343</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>148704</v>
       </c>
       <c r="R109" t="n">
-        <v>79.34</v>
+        <v>79.34050000000001</v>
       </c>
       <c r="S109" t="n">
         <v>9326</v>
@@ -10572,7 +10572,7 @@
         <v>835</v>
       </c>
       <c r="I110" t="n">
-        <v>9.65</v>
+        <v>9.6457</v>
       </c>
       <c r="J110" t="n">
         <v>177800</v>
@@ -10584,7 +10584,7 @@
         <v>12893</v>
       </c>
       <c r="M110" t="n">
-        <v>6.55</v>
+        <v>6.552</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>151241</v>
       </c>
       <c r="R110" t="n">
-        <v>82.25</v>
+        <v>82.24630000000001</v>
       </c>
       <c r="S110" t="n">
         <v>10306</v>
@@ -10662,7 +10662,7 @@
         <v>1215</v>
       </c>
       <c r="I111" t="n">
-        <v>10.21</v>
+        <v>10.2108</v>
       </c>
       <c r="J111" t="n">
         <v>172652</v>
@@ -10674,7 +10674,7 @@
         <v>16466</v>
       </c>
       <c r="M111" t="n">
-        <v>8.56</v>
+        <v>8.5633</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>141394</v>
       </c>
       <c r="R111" t="n">
-        <v>80.42</v>
+        <v>80.41970000000001</v>
       </c>
       <c r="S111" t="n">
         <v>10318</v>
@@ -10752,7 +10752,7 @@
         <v>2038</v>
       </c>
       <c r="I112" t="n">
-        <v>13.99</v>
+        <v>13.9932</v>
       </c>
       <c r="J112" t="n">
         <v>269898</v>
@@ -10764,7 +10764,7 @@
         <v>34372</v>
       </c>
       <c r="M112" t="n">
-        <v>10.95</v>
+        <v>10.9531</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>244319</v>
       </c>
       <c r="R112" t="n">
-        <v>87.43000000000001</v>
+        <v>87.4323</v>
       </c>
       <c r="S112" t="n">
         <v>26312</v>
@@ -10842,7 +10842,7 @@
         <v>2021</v>
       </c>
       <c r="I113" t="n">
-        <v>18.89</v>
+        <v>18.8921</v>
       </c>
       <c r="J113" t="n">
         <v>240742</v>
@@ -10854,7 +10854,7 @@
         <v>46471</v>
       </c>
       <c r="M113" t="n">
-        <v>15.66</v>
+        <v>15.6564</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>231600</v>
       </c>
       <c r="R113" t="n">
-        <v>92.51000000000001</v>
+        <v>92.512</v>
       </c>
       <c r="S113" t="n">
         <v>32458</v>
@@ -10932,7 +10932,7 @@
         <v>2827</v>
       </c>
       <c r="I114" t="n">
-        <v>27.28</v>
+        <v>27.2829</v>
       </c>
       <c r="J114" t="n">
         <v>296011</v>
@@ -10944,7 +10944,7 @@
         <v>96934</v>
       </c>
       <c r="M114" t="n">
-        <v>23.81</v>
+        <v>23.8125</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>263457</v>
       </c>
       <c r="R114" t="n">
-        <v>84.95</v>
+        <v>84.9483</v>
       </c>
       <c r="S114" t="n">
         <v>79742</v>
@@ -11022,7 +11022,7 @@
         <v>2068</v>
       </c>
       <c r="I115" t="n">
-        <v>31.96</v>
+        <v>31.9554</v>
       </c>
       <c r="J115" t="n">
         <v>185282</v>
@@ -11034,7 +11034,7 @@
         <v>78681</v>
       </c>
       <c r="M115" t="n">
-        <v>28.9</v>
+        <v>28.8955</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>179814</v>
       </c>
       <c r="R115" t="n">
-        <v>92.87</v>
+        <v>92.8724</v>
       </c>
       <c r="S115" t="n">
         <v>70835</v>
@@ -11112,7 +11112,7 @@
         <v>5888</v>
       </c>
       <c r="I116" t="n">
-        <v>26.93</v>
+        <v>26.9341</v>
       </c>
       <c r="J116" t="n">
         <v>306290</v>
@@ -11143,7 +11143,7 @@
         <v>301014</v>
       </c>
       <c r="R116" t="n">
-        <v>93.33</v>
+        <v>93.32899999999999</v>
       </c>
       <c r="S116" t="n">
         <v>82443</v>
@@ -11202,7 +11202,7 @@
         <v>2215</v>
       </c>
       <c r="I117" t="n">
-        <v>13.38</v>
+        <v>13.378</v>
       </c>
       <c r="J117" t="n">
         <v>293516</v>
@@ -11214,7 +11214,7 @@
         <v>35306</v>
       </c>
       <c r="M117" t="n">
-        <v>10.42</v>
+        <v>10.4195</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>273544</v>
       </c>
       <c r="R117" t="n">
-        <v>90.12</v>
+        <v>90.1176</v>
       </c>
       <c r="S117" t="n">
         <v>31277</v>
@@ -11292,7 +11292,7 @@
         <v>3550</v>
       </c>
       <c r="I118" t="n">
-        <v>24.71</v>
+        <v>24.7096</v>
       </c>
       <c r="J118" t="n">
         <v>377740</v>
@@ -11304,7 +11304,7 @@
         <v>94204</v>
       </c>
       <c r="M118" t="n">
-        <v>18.78</v>
+        <v>18.7765</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>363991</v>
       </c>
       <c r="R118" t="n">
-        <v>89.31999999999999</v>
+        <v>89.3214</v>
       </c>
       <c r="S118" t="n">
         <v>98349</v>
@@ -11382,7 +11382,7 @@
         <v>2143</v>
       </c>
       <c r="I119" t="n">
-        <v>20.52</v>
+        <v>20.5221</v>
       </c>
       <c r="J119" t="n">
         <v>278531</v>
@@ -11394,7 +11394,7 @@
         <v>58918</v>
       </c>
       <c r="M119" t="n">
-        <v>16.81</v>
+        <v>16.8121</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>226109</v>
       </c>
       <c r="R119" t="n">
-        <v>77.56</v>
+        <v>77.5586</v>
       </c>
       <c r="S119" t="n">
         <v>44501</v>
@@ -11472,7 +11472,7 @@
         <v>3275</v>
       </c>
       <c r="I120" t="n">
-        <v>21.87</v>
+        <v>21.8674</v>
       </c>
       <c r="J120" t="n">
         <v>272946</v>
@@ -11484,7 +11484,7 @@
         <v>61895</v>
       </c>
       <c r="M120" t="n">
-        <v>17.72</v>
+        <v>17.7178</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>258549</v>
       </c>
       <c r="R120" t="n">
-        <v>89.95</v>
+        <v>89.9482</v>
       </c>
       <c r="S120" t="n">
         <v>60176</v>
@@ -11562,7 +11562,7 @@
         <v>1892</v>
       </c>
       <c r="I121" t="n">
-        <v>26.98</v>
+        <v>26.9764</v>
       </c>
       <c r="J121" t="n">
         <v>179308</v>
@@ -11574,7 +11574,7 @@
         <v>59039</v>
       </c>
       <c r="M121" t="n">
-        <v>24.04</v>
+        <v>24.0438</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>156499</v>
       </c>
       <c r="R121" t="n">
-        <v>83.91</v>
+        <v>83.9096</v>
       </c>
       <c r="S121" t="n">
         <v>47016</v>
@@ -11652,7 +11652,7 @@
         <v>2145</v>
       </c>
       <c r="I122" t="n">
-        <v>25.47</v>
+        <v>25.4694</v>
       </c>
       <c r="J122" t="n">
         <v>254422</v>
@@ -11664,7 +11664,7 @@
         <v>75308</v>
       </c>
       <c r="M122" t="n">
-        <v>22.06</v>
+        <v>22.0608</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>221033</v>
       </c>
       <c r="R122" t="n">
-        <v>83.08</v>
+        <v>83.077</v>
       </c>
       <c r="S122" t="n">
         <v>58416</v>
@@ -11742,7 +11742,7 @@
         <v>2593</v>
       </c>
       <c r="I123" t="n">
-        <v>20.51</v>
+        <v>20.5116</v>
       </c>
       <c r="J123" t="n">
         <v>283621</v>
@@ -11754,7 +11754,7 @@
         <v>56322</v>
       </c>
       <c r="M123" t="n">
-        <v>15.78</v>
+        <v>15.785</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>267917</v>
       </c>
       <c r="R123" t="n">
-        <v>89.16</v>
+        <v>89.16119999999999</v>
       </c>
       <c r="S123" t="n">
         <v>52107</v>
@@ -11832,7 +11832,7 @@
         <v>1352</v>
       </c>
       <c r="I124" t="n">
-        <v>14.33</v>
+        <v>14.3328</v>
       </c>
       <c r="J124" t="n">
         <v>196375</v>
@@ -11844,7 +11844,7 @@
         <v>27215</v>
       </c>
       <c r="M124" t="n">
-        <v>11.87</v>
+        <v>11.8724</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>181196</v>
       </c>
       <c r="R124" t="n">
-        <v>89.69</v>
+        <v>89.6943</v>
       </c>
       <c r="S124" t="n">
         <v>21589</v>
@@ -11922,7 +11922,7 @@
         <v>1999</v>
       </c>
       <c r="I125" t="n">
-        <v>15.06</v>
+        <v>15.0634</v>
       </c>
       <c r="J125" t="n">
         <v>168251</v>
@@ -11934,7 +11934,7 @@
         <v>25806</v>
       </c>
       <c r="M125" t="n">
-        <v>13.03</v>
+        <v>13.0274</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>150431</v>
       </c>
       <c r="R125" t="n">
-        <v>87.31999999999999</v>
+        <v>87.31570000000001</v>
       </c>
       <c r="S125" t="n">
         <v>20132</v>
@@ -12012,7 +12012,7 @@
         <v>2914</v>
       </c>
       <c r="I126" t="n">
-        <v>19.01</v>
+        <v>19.0062</v>
       </c>
       <c r="J126" t="n">
         <v>220317</v>
@@ -12024,7 +12024,7 @@
         <v>43493</v>
       </c>
       <c r="M126" t="n">
-        <v>15.99</v>
+        <v>15.9891</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>203575</v>
       </c>
       <c r="R126" t="n">
-        <v>89.08</v>
+        <v>89.0825</v>
       </c>
       <c r="S126" t="n">
         <v>31340</v>
@@ -12102,7 +12102,7 @@
         <v>2901</v>
       </c>
       <c r="I127" t="n">
-        <v>15.03</v>
+        <v>15.0322</v>
       </c>
       <c r="J127" t="n">
         <v>206878</v>
@@ -12114,7 +12114,7 @@
         <v>30736</v>
       </c>
       <c r="M127" t="n">
-        <v>12.62</v>
+        <v>12.6237</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>188249</v>
       </c>
       <c r="R127" t="n">
-        <v>88.48999999999999</v>
+        <v>88.48699999999999</v>
       </c>
       <c r="S127" t="n">
         <v>17133</v>
@@ -12192,7 +12192,7 @@
         <v>2600</v>
       </c>
       <c r="I128" t="n">
-        <v>18.68</v>
+        <v>18.6827</v>
       </c>
       <c r="J128" t="n">
         <v>227090</v>
@@ -12204,7 +12204,7 @@
         <v>41905</v>
       </c>
       <c r="M128" t="n">
-        <v>15.01</v>
+        <v>15.0055</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>208619</v>
       </c>
       <c r="R128" t="n">
-        <v>87.89</v>
+        <v>87.8918</v>
       </c>
       <c r="S128" t="n">
         <v>32957</v>
@@ -12282,7 +12282,7 @@
         <v>2328</v>
       </c>
       <c r="I129" t="n">
-        <v>14.03</v>
+        <v>14.0277</v>
       </c>
       <c r="J129" t="n">
         <v>209156</v>
@@ -12294,7 +12294,7 @@
         <v>25585</v>
       </c>
       <c r="M129" t="n">
-        <v>10.52</v>
+        <v>10.5166</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>201624</v>
       </c>
       <c r="R129" t="n">
-        <v>92.62</v>
+        <v>92.6164</v>
       </c>
       <c r="S129" t="n">
         <v>21460</v>
@@ -12372,7 +12372,7 @@
         <v>3732</v>
       </c>
       <c r="I130" t="n">
-        <v>16.13</v>
+        <v>16.1253</v>
       </c>
       <c r="J130" t="n">
         <v>250423</v>
@@ -12384,7 +12384,7 @@
         <v>38722</v>
       </c>
       <c r="M130" t="n">
-        <v>12.97</v>
+        <v>12.9692</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>237183</v>
       </c>
       <c r="R130" t="n">
-        <v>91.28</v>
+        <v>91.2783</v>
       </c>
       <c r="S130" t="n">
         <v>28588</v>
@@ -12462,7 +12462,7 @@
         <v>3282</v>
       </c>
       <c r="I131" t="n">
-        <v>16.5</v>
+        <v>16.4999</v>
       </c>
       <c r="J131" t="n">
         <v>211788</v>
@@ -12474,7 +12474,7 @@
         <v>34561</v>
       </c>
       <c r="M131" t="n">
-        <v>13.63</v>
+        <v>13.6261</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>197593</v>
       </c>
       <c r="R131" t="n">
-        <v>90.19</v>
+        <v>90.1934</v>
       </c>
       <c r="S131" t="n">
         <v>23872</v>
@@ -12564,7 +12564,7 @@
         <v>36553</v>
       </c>
       <c r="M132" t="n">
-        <v>12.38</v>
+        <v>12.3843</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>239140</v>
       </c>
       <c r="R132" t="n">
-        <v>92.47</v>
+        <v>92.4738</v>
       </c>
       <c r="S132" t="n">
         <v>28567</v>
@@ -12642,7 +12642,7 @@
         <v>2069</v>
       </c>
       <c r="I133" t="n">
-        <v>20.95</v>
+        <v>20.9524</v>
       </c>
       <c r="J133" t="n">
         <v>228223</v>
@@ -12654,7 +12654,7 @@
         <v>51037</v>
       </c>
       <c r="M133" t="n">
-        <v>17.68</v>
+        <v>17.6772</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>212024</v>
       </c>
       <c r="R133" t="n">
-        <v>89.20999999999999</v>
+        <v>89.206</v>
       </c>
       <c r="S133" t="n">
         <v>36092</v>
@@ -12732,7 +12732,7 @@
         <v>2036</v>
       </c>
       <c r="I134" t="n">
-        <v>15.22</v>
+        <v>15.2171</v>
       </c>
       <c r="J134" t="n">
         <v>233850</v>
@@ -12744,7 +12744,7 @@
         <v>34009</v>
       </c>
       <c r="M134" t="n">
-        <v>12.33</v>
+        <v>12.3301</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>226554</v>
       </c>
       <c r="R134" t="n">
-        <v>93.69</v>
+        <v>93.68980000000001</v>
       </c>
       <c r="S134" t="n">
         <v>25386</v>
@@ -12822,7 +12822,7 @@
         <v>506</v>
       </c>
       <c r="I135" t="n">
-        <v>10.55</v>
+        <v>10.5507</v>
       </c>
       <c r="J135" t="n">
         <v>189697</v>
@@ -12834,7 +12834,7 @@
         <v>17567</v>
       </c>
       <c r="M135" t="n">
-        <v>8.279999999999999</v>
+        <v>8.2835</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>181078</v>
       </c>
       <c r="R135" t="n">
-        <v>93.09999999999999</v>
+        <v>93.0968</v>
       </c>
       <c r="S135" t="n">
         <v>15084</v>
@@ -12912,7 +12912,7 @@
         <v>388</v>
       </c>
       <c r="I136" t="n">
-        <v>9.99</v>
+        <v>9.994300000000001</v>
       </c>
       <c r="J136" t="n">
         <v>216777</v>
@@ -12924,7 +12924,7 @@
         <v>14264</v>
       </c>
       <c r="M136" t="n">
-        <v>5.92</v>
+        <v>5.9224</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>216829</v>
       </c>
       <c r="R136" t="n">
-        <v>95.69</v>
+        <v>95.6948</v>
       </c>
       <c r="S136" t="n">
         <v>18896</v>
@@ -13002,7 +13002,7 @@
         <v>594</v>
       </c>
       <c r="I137" t="n">
-        <v>8.050000000000001</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="J137" t="n">
         <v>196751</v>
@@ -13014,7 +13014,7 @@
         <v>11896</v>
       </c>
       <c r="M137" t="n">
-        <v>5.56</v>
+        <v>5.5593</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>189357</v>
       </c>
       <c r="R137" t="n">
-        <v>93.7</v>
+        <v>93.7007</v>
       </c>
       <c r="S137" t="n">
         <v>10059</v>
@@ -13092,7 +13092,7 @@
         <v>807</v>
       </c>
       <c r="I138" t="n">
-        <v>6.92</v>
+        <v>6.9179</v>
       </c>
       <c r="J138" t="n">
         <v>215447</v>
@@ -13104,7 +13104,7 @@
         <v>9471</v>
       </c>
       <c r="M138" t="n">
-        <v>4.09</v>
+        <v>4.0919</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>209091</v>
       </c>
       <c r="R138" t="n">
-        <v>94.19</v>
+        <v>94.1902</v>
       </c>
       <c r="S138" t="n">
         <v>8644</v>
@@ -13182,7 +13182,7 @@
         <v>2183</v>
       </c>
       <c r="I139" t="n">
-        <v>10.97</v>
+        <v>10.9726</v>
       </c>
       <c r="J139" t="n">
         <v>256674</v>
@@ -13194,7 +13194,7 @@
         <v>22290</v>
       </c>
       <c r="M139" t="n">
-        <v>7.73</v>
+        <v>7.7313</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>241216</v>
       </c>
       <c r="R139" t="n">
-        <v>90.68000000000001</v>
+        <v>90.67619999999999</v>
       </c>
       <c r="S139" t="n">
         <v>17879</v>
@@ -13272,7 +13272,7 @@
         <v>1616</v>
       </c>
       <c r="I140" t="n">
-        <v>13.98</v>
+        <v>13.9847</v>
       </c>
       <c r="J140" t="n">
         <v>271539</v>
@@ -13284,7 +13284,7 @@
         <v>31825</v>
       </c>
       <c r="M140" t="n">
-        <v>10.08</v>
+        <v>10.0812</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>254985</v>
       </c>
       <c r="R140" t="n">
-        <v>89.83</v>
+        <v>89.8271</v>
       </c>
       <c r="S140" t="n">
         <v>27341</v>
@@ -13362,7 +13362,7 @@
         <v>629</v>
       </c>
       <c r="I141" t="n">
-        <v>20.62</v>
+        <v>20.616</v>
       </c>
       <c r="J141" t="n">
         <v>220789</v>
@@ -13374,7 +13374,7 @@
         <v>42225</v>
       </c>
       <c r="M141" t="n">
-        <v>15.18</v>
+        <v>15.1819</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>196347</v>
       </c>
       <c r="R141" t="n">
-        <v>83.23</v>
+        <v>83.2321</v>
       </c>
       <c r="S141" t="n">
         <v>37262</v>
@@ -13452,7 +13452,7 @@
         <v>826</v>
       </c>
       <c r="I142" t="n">
-        <v>22.12</v>
+        <v>22.1197</v>
       </c>
       <c r="J142" t="n">
         <v>203555</v>
@@ -13464,7 +13464,7 @@
         <v>43972</v>
       </c>
       <c r="M142" t="n">
-        <v>16.82</v>
+        <v>16.8237</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>182493</v>
       </c>
       <c r="R142" t="n">
-        <v>83.94</v>
+        <v>83.94459999999999</v>
       </c>
       <c r="S142" t="n">
         <v>37096</v>
@@ -13542,7 +13542,7 @@
         <v>1445</v>
       </c>
       <c r="I143" t="n">
-        <v>14.11</v>
+        <v>14.114</v>
       </c>
       <c r="J143" t="n">
         <v>243304</v>
@@ -13554,7 +13554,7 @@
         <v>27048</v>
       </c>
       <c r="M143" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5479</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>213583</v>
       </c>
       <c r="R143" t="n">
-        <v>83.34999999999999</v>
+        <v>83.35299999999999</v>
       </c>
       <c r="S143" t="n">
         <v>23331</v>
@@ -13632,7 +13632,7 @@
         <v>731</v>
       </c>
       <c r="I144" t="n">
-        <v>8.609999999999999</v>
+        <v>8.613899999999999</v>
       </c>
       <c r="J144" t="n">
         <v>204885</v>
@@ -13644,7 +13644,7 @@
         <v>13154</v>
       </c>
       <c r="M144" t="n">
-        <v>5.87</v>
+        <v>5.8672</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>185213</v>
       </c>
       <c r="R144" t="n">
-        <v>87.76000000000001</v>
+        <v>87.7608</v>
       </c>
       <c r="S144" t="n">
         <v>8128</v>
@@ -13722,7 +13722,7 @@
         <v>780</v>
       </c>
       <c r="I145" t="n">
-        <v>12.91</v>
+        <v>12.9094</v>
       </c>
       <c r="J145" t="n">
         <v>227161</v>
@@ -13734,7 +13734,7 @@
         <v>26616</v>
       </c>
       <c r="M145" t="n">
-        <v>10.2</v>
+        <v>10.2042</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>209780</v>
       </c>
       <c r="R145" t="n">
-        <v>89.56999999999999</v>
+        <v>89.5665</v>
       </c>
       <c r="S145" t="n">
         <v>14031</v>
@@ -13812,7 +13812,7 @@
         <v>892</v>
       </c>
       <c r="I146" t="n">
-        <v>9.49</v>
+        <v>9.486000000000001</v>
       </c>
       <c r="J146" t="n">
         <v>206553</v>
@@ -13824,7 +13824,7 @@
         <v>15588</v>
       </c>
       <c r="M146" t="n">
-        <v>6.83</v>
+        <v>6.8309</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>189141</v>
       </c>
       <c r="R146" t="n">
-        <v>88.95999999999999</v>
+        <v>88.9606</v>
       </c>
       <c r="S146" t="n">
         <v>8353</v>
@@ -13902,7 +13902,7 @@
         <v>703</v>
       </c>
       <c r="I147" t="n">
-        <v>11.46</v>
+        <v>11.4597</v>
       </c>
       <c r="J147" t="n">
         <v>202720</v>
@@ -13914,7 +13914,7 @@
         <v>19947</v>
       </c>
       <c r="M147" t="n">
-        <v>8.710000000000001</v>
+        <v>8.7121</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>184426</v>
       </c>
       <c r="R147" t="n">
-        <v>88.23999999999999</v>
+        <v>88.2375</v>
       </c>
       <c r="S147" t="n">
         <v>12011</v>
@@ -13992,7 +13992,7 @@
         <v>1725</v>
       </c>
       <c r="I148" t="n">
-        <v>9.48</v>
+        <v>9.4779</v>
       </c>
       <c r="J148" t="n">
         <v>280566</v>
@@ -14004,7 +14004,7 @@
         <v>21493</v>
       </c>
       <c r="M148" t="n">
-        <v>6.93</v>
+        <v>6.9345</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>253654</v>
       </c>
       <c r="R148" t="n">
-        <v>87.94</v>
+        <v>87.9372</v>
       </c>
       <c r="S148" t="n">
         <v>14431</v>
@@ -14082,7 +14082,7 @@
         <v>1801</v>
       </c>
       <c r="I149" t="n">
-        <v>7.19</v>
+        <v>7.1902</v>
       </c>
       <c r="J149" t="n">
         <v>260376</v>
@@ -14094,7 +14094,7 @@
         <v>13866</v>
       </c>
       <c r="M149" t="n">
-        <v>4.94</v>
+        <v>4.9425</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>230570</v>
       </c>
       <c r="R149" t="n">
-        <v>86.45999999999999</v>
+        <v>86.4588</v>
       </c>
       <c r="S149" t="n">
         <v>8799</v>
@@ -14172,7 +14172,7 @@
         <v>713</v>
       </c>
       <c r="I150" t="n">
-        <v>4.89</v>
+        <v>4.8945</v>
       </c>
       <c r="J150" t="n">
         <v>252333</v>
@@ -14184,7 +14184,7 @@
         <v>4158</v>
       </c>
       <c r="M150" t="n">
-        <v>1.57</v>
+        <v>1.5672</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>235858</v>
       </c>
       <c r="R150" t="n">
-        <v>90.31</v>
+        <v>90.3113</v>
       </c>
       <c r="S150" t="n">
         <v>6119</v>
@@ -14262,7 +14262,7 @@
         <v>799</v>
       </c>
       <c r="I151" t="n">
-        <v>4.29</v>
+        <v>4.2859</v>
       </c>
       <c r="J151" t="n">
         <v>254189</v>
@@ -14274,7 +14274,7 @@
         <v>3778</v>
       </c>
       <c r="M151" t="n">
-        <v>1.42</v>
+        <v>1.4226</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>228548</v>
       </c>
       <c r="R151" t="n">
-        <v>87.3</v>
+        <v>87.301</v>
       </c>
       <c r="S151" t="n">
         <v>4627</v>
@@ -14352,7 +14352,7 @@
         <v>1151</v>
       </c>
       <c r="I152" t="n">
-        <v>9.880000000000001</v>
+        <v>9.8757</v>
       </c>
       <c r="J152" t="n">
         <v>200541</v>
@@ -14364,7 +14364,7 @@
         <v>15746</v>
       </c>
       <c r="M152" t="n">
-        <v>7.08</v>
+        <v>7.0763</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>175754</v>
       </c>
       <c r="R152" t="n">
-        <v>85</v>
+        <v>84.99979999999999</v>
       </c>
       <c r="S152" t="n">
         <v>12146</v>
@@ -14442,7 +14442,7 @@
         <v>1198</v>
       </c>
       <c r="I153" t="n">
-        <v>12.22</v>
+        <v>12.223</v>
       </c>
       <c r="J153" t="n">
         <v>228537</v>
@@ -14454,7 +14454,7 @@
         <v>22525</v>
       </c>
       <c r="M153" t="n">
-        <v>8.65</v>
+        <v>8.651400000000001</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>209186</v>
       </c>
       <c r="R153" t="n">
-        <v>87.95</v>
+        <v>87.9539</v>
       </c>
       <c r="S153" t="n">
         <v>20677</v>
@@ -14532,7 +14532,7 @@
         <v>849</v>
       </c>
       <c r="I154" t="n">
-        <v>12.81</v>
+        <v>12.8129</v>
       </c>
       <c r="J154" t="n">
         <v>179955</v>
@@ -14544,7 +14544,7 @@
         <v>17377</v>
       </c>
       <c r="M154" t="n">
-        <v>8.42</v>
+        <v>8.419</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>168780</v>
       </c>
       <c r="R154" t="n">
-        <v>89.29000000000001</v>
+        <v>89.2902</v>
       </c>
       <c r="S154" t="n">
         <v>16824</v>
@@ -14622,7 +14622,7 @@
         <v>1195</v>
       </c>
       <c r="I155" t="n">
-        <v>8.880000000000001</v>
+        <v>8.883599999999999</v>
       </c>
       <c r="J155" t="n">
         <v>233247</v>
@@ -14634,7 +14634,7 @@
         <v>15940</v>
       </c>
       <c r="M155" t="n">
-        <v>6.23</v>
+        <v>6.2269</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>210767</v>
       </c>
       <c r="R155" t="n">
-        <v>87.8</v>
+        <v>87.80200000000001</v>
       </c>
       <c r="S155" t="n">
         <v>11151</v>
@@ -14712,7 +14712,7 @@
         <v>1176</v>
       </c>
       <c r="I156" t="n">
-        <v>13.58</v>
+        <v>13.5806</v>
       </c>
       <c r="J156" t="n">
         <v>213392</v>
@@ -14724,7 +14724,7 @@
         <v>25774</v>
       </c>
       <c r="M156" t="n">
-        <v>10.44</v>
+        <v>10.4379</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>190378</v>
       </c>
       <c r="R156" t="n">
-        <v>86.08</v>
+        <v>86.0847</v>
       </c>
       <c r="S156" t="n">
         <v>19162</v>
@@ -14802,7 +14802,7 @@
         <v>1507</v>
       </c>
       <c r="I157" t="n">
-        <v>9.83</v>
+        <v>9.827</v>
       </c>
       <c r="J157" t="n">
         <v>228860</v>
@@ -14814,7 +14814,7 @@
         <v>17504</v>
       </c>
       <c r="M157" t="n">
-        <v>6.9</v>
+        <v>6.8967</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>213965</v>
       </c>
       <c r="R157" t="n">
-        <v>90.55</v>
+        <v>90.5492</v>
       </c>
       <c r="S157" t="n">
         <v>12946</v>
@@ -14892,7 +14892,7 @@
         <v>1448</v>
       </c>
       <c r="I158" t="n">
-        <v>13.54</v>
+        <v>13.5431</v>
       </c>
       <c r="J158" t="n">
         <v>223530</v>
@@ -14904,7 +14904,7 @@
         <v>27577</v>
       </c>
       <c r="M158" t="n">
-        <v>10.67</v>
+        <v>10.6662</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>207310</v>
       </c>
       <c r="R158" t="n">
-        <v>89.76000000000001</v>
+        <v>89.75700000000001</v>
       </c>
       <c r="S158" t="n">
         <v>19327</v>
@@ -14982,7 +14982,7 @@
         <v>1322</v>
       </c>
       <c r="I159" t="n">
-        <v>12.5</v>
+        <v>12.4963</v>
       </c>
       <c r="J159" t="n">
         <v>220106</v>
@@ -14994,7 +14994,7 @@
         <v>22403</v>
       </c>
       <c r="M159" t="n">
-        <v>8.91</v>
+        <v>8.9064</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>196586</v>
       </c>
       <c r="R159" t="n">
-        <v>85.79000000000001</v>
+        <v>85.7945</v>
       </c>
       <c r="S159" t="n">
         <v>18332</v>
@@ -15072,7 +15072,7 @@
         <v>998</v>
       </c>
       <c r="I160" t="n">
-        <v>7.96</v>
+        <v>7.9617</v>
       </c>
       <c r="J160" t="n">
         <v>218591</v>
@@ -15084,7 +15084,7 @@
         <v>12935</v>
       </c>
       <c r="M160" t="n">
-        <v>5.45</v>
+        <v>5.4463</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>187905</v>
       </c>
       <c r="R160" t="n">
-        <v>83.68000000000001</v>
+        <v>83.6751</v>
       </c>
       <c r="S160" t="n">
         <v>7572</v>
@@ -15162,7 +15162,7 @@
         <v>1313</v>
       </c>
       <c r="I161" t="n">
-        <v>9.67</v>
+        <v>9.674899999999999</v>
       </c>
       <c r="J161" t="n">
         <v>232766</v>
@@ -15174,7 +15174,7 @@
         <v>18229</v>
       </c>
       <c r="M161" t="n">
-        <v>7.07</v>
+        <v>7.0738</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>200448</v>
       </c>
       <c r="R161" t="n">
-        <v>83.70999999999999</v>
+        <v>83.7052</v>
       </c>
       <c r="S161" t="n">
         <v>11114</v>
@@ -15252,7 +15252,7 @@
         <v>1075</v>
       </c>
       <c r="I162" t="n">
-        <v>7.82</v>
+        <v>7.8212</v>
       </c>
       <c r="J162" t="n">
         <v>225840</v>
@@ -15264,7 +15264,7 @@
         <v>12384</v>
       </c>
       <c r="M162" t="n">
-        <v>5.05</v>
+        <v>5.0547</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>188461</v>
       </c>
       <c r="R162" t="n">
-        <v>81.02</v>
+        <v>81.01739999999999</v>
       </c>
       <c r="S162" t="n">
         <v>7881</v>
@@ -15342,7 +15342,7 @@
         <v>1749</v>
       </c>
       <c r="I163" t="n">
-        <v>11.14</v>
+        <v>11.141</v>
       </c>
       <c r="J163" t="n">
         <v>249516</v>
@@ -15354,7 +15354,7 @@
         <v>23671</v>
       </c>
       <c r="M163" t="n">
-        <v>8.43</v>
+        <v>8.4298</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>219324</v>
       </c>
       <c r="R163" t="n">
-        <v>85.3</v>
+        <v>85.29730000000001</v>
       </c>
       <c r="S163" t="n">
         <v>14939</v>
@@ -15432,7 +15432,7 @@
         <v>1438</v>
       </c>
       <c r="I164" t="n">
-        <v>15.05</v>
+        <v>15.0542</v>
       </c>
       <c r="J164" t="n">
         <v>165979</v>
@@ -15444,7 +15444,7 @@
         <v>22415</v>
       </c>
       <c r="M164" t="n">
-        <v>11.47</v>
+        <v>11.4717</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>151326</v>
       </c>
       <c r="R164" t="n">
-        <v>87.48</v>
+        <v>87.4823</v>
       </c>
       <c r="S164" t="n">
         <v>18740</v>
@@ -15522,7 +15522,7 @@
         <v>951</v>
       </c>
       <c r="I165" t="n">
-        <v>8.02</v>
+        <v>8.018700000000001</v>
       </c>
       <c r="J165" t="n">
         <v>163598</v>
@@ -15534,7 +15534,7 @@
         <v>8926</v>
       </c>
       <c r="M165" t="n">
-        <v>5.02</v>
+        <v>5.0186</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>151637</v>
       </c>
       <c r="R165" t="n">
-        <v>89.76000000000001</v>
+        <v>89.7611</v>
       </c>
       <c r="S165" t="n">
         <v>8528</v>
@@ -15612,7 +15612,7 @@
         <v>859</v>
       </c>
       <c r="I166" t="n">
-        <v>7.02</v>
+        <v>7.0245</v>
       </c>
       <c r="J166" t="n">
         <v>180815</v>
@@ -15624,7 +15624,7 @@
         <v>8442</v>
       </c>
       <c r="M166" t="n">
-        <v>4.34</v>
+        <v>4.3409</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>162216</v>
       </c>
       <c r="R166" t="n">
-        <v>87.2</v>
+        <v>87.197</v>
       </c>
       <c r="S166" t="n">
         <v>7223</v>
@@ -15702,7 +15702,7 @@
         <v>1325</v>
       </c>
       <c r="I167" t="n">
-        <v>10.57</v>
+        <v>10.5671</v>
       </c>
       <c r="J167" t="n">
         <v>217786</v>
@@ -15714,7 +15714,7 @@
         <v>18156</v>
       </c>
       <c r="M167" t="n">
-        <v>7.46</v>
+        <v>7.4557</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>191030</v>
       </c>
       <c r="R167" t="n">
-        <v>84.77</v>
+        <v>84.7655</v>
       </c>
       <c r="S167" t="n">
         <v>13444</v>
@@ -15792,7 +15792,7 @@
         <v>1089</v>
       </c>
       <c r="I168" t="n">
-        <v>14.18</v>
+        <v>14.1791</v>
       </c>
       <c r="J168" t="n">
         <v>223475</v>
@@ -15804,7 +15804,7 @@
         <v>28462</v>
       </c>
       <c r="M168" t="n">
-        <v>10.93</v>
+        <v>10.9302</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>194100</v>
       </c>
       <c r="R168" t="n">
-        <v>83.69</v>
+        <v>83.6872</v>
       </c>
       <c r="S168" t="n">
         <v>21072</v>
@@ -15882,7 +15882,7 @@
         <v>1533</v>
       </c>
       <c r="I169" t="n">
-        <v>13.22</v>
+        <v>13.2197</v>
       </c>
       <c r="J169" t="n">
         <v>249036</v>
@@ -15894,7 +15894,7 @@
         <v>29081</v>
       </c>
       <c r="M169" t="n">
-        <v>10.13</v>
+        <v>10.1337</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>217875</v>
       </c>
       <c r="R169" t="n">
-        <v>84.48</v>
+        <v>84.483</v>
       </c>
       <c r="S169" t="n">
         <v>20855</v>
@@ -15972,7 +15972,7 @@
         <v>1403</v>
       </c>
       <c r="I170" t="n">
-        <v>10.15</v>
+        <v>10.1472</v>
       </c>
       <c r="J170" t="n">
         <v>255800</v>
@@ -15984,7 +15984,7 @@
         <v>20226</v>
       </c>
       <c r="M170" t="n">
-        <v>7.1</v>
+        <v>7.1046</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>231444</v>
       </c>
       <c r="R170" t="n">
-        <v>87.52</v>
+        <v>87.515</v>
       </c>
       <c r="S170" t="n">
         <v>14714</v>
@@ -16062,7 +16062,7 @@
         <v>843</v>
       </c>
       <c r="I171" t="n">
-        <v>8.31</v>
+        <v>8.3125</v>
       </c>
       <c r="J171" t="n">
         <v>248012</v>
@@ -16074,7 +16074,7 @@
         <v>16044</v>
       </c>
       <c r="M171" t="n">
-        <v>5.93</v>
+        <v>5.9313</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>208944</v>
       </c>
       <c r="R171" t="n">
-        <v>82.11</v>
+        <v>82.11499999999999</v>
       </c>
       <c r="S171" t="n">
         <v>5021</v>
@@ -16152,7 +16152,7 @@
         <v>915</v>
       </c>
       <c r="I172" t="n">
-        <v>11.65</v>
+        <v>11.647</v>
       </c>
       <c r="J172" t="n">
         <v>243129</v>
@@ -16164,7 +16164,7 @@
         <v>23311</v>
       </c>
       <c r="M172" t="n">
-        <v>8.470000000000001</v>
+        <v>8.4712</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>208288</v>
       </c>
       <c r="R172" t="n">
-        <v>82.7</v>
+        <v>82.6973</v>
       </c>
       <c r="S172" t="n">
         <v>15705</v>
@@ -16242,7 +16242,7 @@
         <v>930</v>
       </c>
       <c r="I173" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1966</v>
       </c>
       <c r="J173" t="n">
         <v>247345</v>
@@ -16254,7 +16254,7 @@
         <v>14777</v>
       </c>
       <c r="M173" t="n">
-        <v>5.48</v>
+        <v>5.4846</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>207723</v>
       </c>
       <c r="R173" t="n">
-        <v>81.56999999999999</v>
+        <v>81.57129999999999</v>
       </c>
       <c r="S173" t="n">
         <v>5739</v>
@@ -16332,7 +16332,7 @@
         <v>940</v>
       </c>
       <c r="I174" t="n">
-        <v>9.59</v>
+        <v>9.594799999999999</v>
       </c>
       <c r="J174" t="n">
         <v>249672</v>
@@ -16344,7 +16344,7 @@
         <v>19793</v>
       </c>
       <c r="M174" t="n">
-        <v>7.17</v>
+        <v>7.167</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>222111</v>
       </c>
       <c r="R174" t="n">
-        <v>86.63</v>
+        <v>86.6345</v>
       </c>
       <c r="S174" t="n">
         <v>9927</v>
@@ -16422,7 +16422,7 @@
         <v>1313</v>
       </c>
       <c r="I175" t="n">
-        <v>15.52</v>
+        <v>15.5192</v>
       </c>
       <c r="J175" t="n">
         <v>237581</v>
@@ -16434,7 +16434,7 @@
         <v>32161</v>
       </c>
       <c r="M175" t="n">
-        <v>11.44</v>
+        <v>11.436</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>198798</v>
       </c>
       <c r="R175" t="n">
-        <v>79.81999999999999</v>
+        <v>79.818</v>
       </c>
       <c r="S175" t="n">
         <v>25191</v>
@@ -16512,7 +16512,7 @@
         <v>1248</v>
       </c>
       <c r="I176" t="n">
-        <v>11.07</v>
+        <v>11.066</v>
       </c>
       <c r="J176" t="n">
         <v>225372</v>
@@ -16524,7 +16524,7 @@
         <v>22164</v>
       </c>
       <c r="M176" t="n">
-        <v>8.75</v>
+        <v>8.7461</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>195304</v>
       </c>
       <c r="R176" t="n">
-        <v>84.45999999999999</v>
+        <v>84.4554</v>
       </c>
       <c r="S176" t="n">
         <v>9793</v>
@@ -16602,7 +16602,7 @@
         <v>826</v>
       </c>
       <c r="I177" t="n">
-        <v>6.8</v>
+        <v>6.7975</v>
       </c>
       <c r="J177" t="n">
         <v>234297</v>
@@ -16614,7 +16614,7 @@
         <v>10431</v>
       </c>
       <c r="M177" t="n">
-        <v>4.15</v>
+        <v>4.1494</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>183745</v>
       </c>
       <c r="R177" t="n">
-        <v>76.26000000000001</v>
+        <v>76.2573</v>
       </c>
       <c r="S177" t="n">
         <v>4293</v>
@@ -16692,7 +16692,7 @@
         <v>974</v>
       </c>
       <c r="I178" t="n">
-        <v>6.6</v>
+        <v>6.6035</v>
       </c>
       <c r="J178" t="n">
         <v>206650</v>
@@ -16704,7 +16704,7 @@
         <v>8435</v>
       </c>
       <c r="M178" t="n">
-        <v>3.81</v>
+        <v>3.8122</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>176274</v>
       </c>
       <c r="R178" t="n">
-        <v>82.83</v>
+        <v>82.8254</v>
       </c>
       <c r="S178" t="n">
         <v>4039</v>
@@ -16782,7 +16782,7 @@
         <v>1176</v>
       </c>
       <c r="I179" t="n">
-        <v>10.57</v>
+        <v>10.5705</v>
       </c>
       <c r="J179" t="n">
         <v>188047</v>
@@ -16794,7 +16794,7 @@
         <v>15542</v>
       </c>
       <c r="M179" t="n">
-        <v>7.39</v>
+        <v>7.3913</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>167618</v>
       </c>
       <c r="R179" t="n">
-        <v>86.08</v>
+        <v>86.0762</v>
       </c>
       <c r="S179" t="n">
         <v>10425</v>
@@ -16872,7 +16872,7 @@
         <v>2034</v>
       </c>
       <c r="I180" t="n">
-        <v>7.37</v>
+        <v>7.3737</v>
       </c>
       <c r="J180" t="n">
         <v>214854</v>
@@ -16884,7 +16884,7 @@
         <v>8874</v>
       </c>
       <c r="M180" t="n">
-        <v>3.83</v>
+        <v>3.8257</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>1195</v>
       </c>
       <c r="I181" t="n">
-        <v>14.62</v>
+        <v>14.6179</v>
       </c>
       <c r="J181" t="n">
         <v>215915</v>
@@ -16974,7 +16974,7 @@
         <v>28953</v>
       </c>
       <c r="M181" t="n">
-        <v>11.45</v>
+        <v>11.4493</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>190378</v>
       </c>
       <c r="R181" t="n">
-        <v>85.02</v>
+        <v>85.0175</v>
       </c>
       <c r="S181" t="n">
         <v>21380</v>
@@ -17052,7 +17052,7 @@
         <v>1701</v>
       </c>
       <c r="I182" t="n">
-        <v>11.6</v>
+        <v>11.6049</v>
       </c>
       <c r="J182" t="n">
         <v>213109</v>
@@ -17064,7 +17064,7 @@
         <v>21808</v>
       </c>
       <c r="M182" t="n">
-        <v>9.050000000000001</v>
+        <v>9.0457</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>182612</v>
       </c>
       <c r="R182" t="n">
-        <v>83.28</v>
+        <v>83.2784</v>
       </c>
       <c r="S182" t="n">
         <v>13629</v>
@@ -17142,7 +17142,7 @@
         <v>1550</v>
       </c>
       <c r="I183" t="n">
-        <v>6.92</v>
+        <v>6.9194</v>
       </c>
       <c r="J183" t="n">
         <v>204081</v>
@@ -17154,7 +17154,7 @@
         <v>8956</v>
       </c>
       <c r="M183" t="n">
-        <v>4.08</v>
+        <v>4.0848</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>180483</v>
       </c>
       <c r="R183" t="n">
-        <v>85.81999999999999</v>
+        <v>85.8233</v>
       </c>
       <c r="S183" t="n">
         <v>6337</v>
@@ -17232,7 +17232,7 @@
         <v>1291</v>
       </c>
       <c r="I184" t="n">
-        <v>8.44</v>
+        <v>8.4392</v>
       </c>
       <c r="J184" t="n">
         <v>218519</v>
@@ -17244,7 +17244,7 @@
         <v>11072</v>
       </c>
       <c r="M184" t="n">
-        <v>4.64</v>
+        <v>4.6392</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>182730</v>
       </c>
       <c r="R184" t="n">
-        <v>80.29000000000001</v>
+        <v>80.2898</v>
       </c>
       <c r="S184" t="n">
         <v>9330</v>
@@ -17334,7 +17334,7 @@
         <v>23018</v>
       </c>
       <c r="M185" t="n">
-        <v>7.05</v>
+        <v>7.0523</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>229267</v>
       </c>
       <c r="R185" t="n">
-        <v>75.56999999999999</v>
+        <v>75.5731</v>
       </c>
       <c r="S185" t="n">
         <v>11857</v>
@@ -17412,7 +17412,7 @@
         <v>2256</v>
       </c>
       <c r="I186" t="n">
-        <v>13.47</v>
+        <v>13.4652</v>
       </c>
       <c r="J186" t="n">
         <v>265474</v>
@@ -17424,7 +17424,7 @@
         <v>33327</v>
       </c>
       <c r="M186" t="n">
-        <v>10.86</v>
+        <v>10.8634</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>215710</v>
       </c>
       <c r="R186" t="n">
-        <v>78.88</v>
+        <v>78.88290000000001</v>
       </c>
       <c r="S186" t="n">
         <v>17344</v>
@@ -17502,7 +17502,7 @@
         <v>1493</v>
       </c>
       <c r="I187" t="n">
-        <v>12.75</v>
+        <v>12.7468</v>
       </c>
       <c r="J187" t="n">
         <v>269088</v>
@@ -17514,7 +17514,7 @@
         <v>32243</v>
       </c>
       <c r="M187" t="n">
-        <v>10.45</v>
+        <v>10.455</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>214067</v>
       </c>
       <c r="R187" t="n">
-        <v>77.52</v>
+        <v>77.5167</v>
       </c>
       <c r="S187" t="n">
         <v>14694</v>
@@ -17592,7 +17592,7 @@
         <v>1259</v>
       </c>
       <c r="I188" t="n">
-        <v>12.94</v>
+        <v>12.9379</v>
       </c>
       <c r="J188" t="n">
         <v>251054</v>
@@ -17604,7 +17604,7 @@
         <v>30746</v>
       </c>
       <c r="M188" t="n">
-        <v>10.66</v>
+        <v>10.6623</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>208643</v>
       </c>
       <c r="R188" t="n">
-        <v>80.98999999999999</v>
+        <v>80.98990000000001</v>
       </c>
       <c r="S188" t="n">
         <v>16447</v>
@@ -17682,7 +17682,7 @@
         <v>1161</v>
       </c>
       <c r="I189" t="n">
-        <v>11.56</v>
+        <v>11.5625</v>
       </c>
       <c r="J189" t="n">
         <v>220931</v>
@@ -17694,7 +17694,7 @@
         <v>22027</v>
       </c>
       <c r="M189" t="n">
-        <v>8.82</v>
+        <v>8.817299999999999</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>190726</v>
       </c>
       <c r="R189" t="n">
-        <v>83.73</v>
+        <v>83.72920000000001</v>
       </c>
       <c r="S189" t="n">
         <v>19861</v>
@@ -17772,7 +17772,7 @@
         <v>1162</v>
       </c>
       <c r="I190" t="n">
-        <v>10.11</v>
+        <v>10.1069</v>
       </c>
       <c r="J190" t="n">
         <v>316225</v>
@@ -17784,7 +17784,7 @@
         <v>20786</v>
       </c>
       <c r="M190" t="n">
-        <v>5.91</v>
+        <v>5.9088</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>271566</v>
       </c>
       <c r="R190" t="n">
-        <v>82.05</v>
+        <v>82.0458</v>
       </c>
       <c r="S190" t="n">
         <v>20380</v>
@@ -17862,7 +17862,7 @@
         <v>1095</v>
       </c>
       <c r="I191" t="n">
-        <v>10.01</v>
+        <v>10.0102</v>
       </c>
       <c r="J191" t="n">
         <v>206567</v>
@@ -17874,7 +17874,7 @@
         <v>17043</v>
       </c>
       <c r="M191" t="n">
-        <v>7.42</v>
+        <v>7.4247</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>189080</v>
       </c>
       <c r="R191" t="n">
-        <v>88.98</v>
+        <v>88.97799999999999</v>
       </c>
       <c r="S191" t="n">
         <v>13134</v>
@@ -17952,7 +17952,7 @@
         <v>524</v>
       </c>
       <c r="I192" t="n">
-        <v>14.9</v>
+        <v>14.8991</v>
       </c>
       <c r="J192" t="n">
         <v>208749</v>
@@ -17964,7 +17964,7 @@
         <v>26577</v>
       </c>
       <c r="M192" t="n">
-        <v>10.83</v>
+        <v>10.8347</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>161801</v>
       </c>
       <c r="R192" t="n">
-        <v>73.98</v>
+        <v>73.97669999999999</v>
       </c>
       <c r="S192" t="n">
         <v>21927</v>
@@ -18042,7 +18042,7 @@
         <v>525</v>
       </c>
       <c r="I193" t="n">
-        <v>24.91</v>
+        <v>24.9086</v>
       </c>
       <c r="J193" t="n">
         <v>168098</v>
@@ -18054,7 +18054,7 @@
         <v>46253</v>
       </c>
       <c r="M193" t="n">
-        <v>20.66</v>
+        <v>20.6618</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>141503</v>
       </c>
       <c r="R193" t="n">
-        <v>79.67</v>
+        <v>79.6729</v>
       </c>
       <c r="S193" t="n">
         <v>37475</v>
@@ -18132,7 +18132,7 @@
         <v>917</v>
       </c>
       <c r="I194" t="n">
-        <v>16.23</v>
+        <v>16.2276</v>
       </c>
       <c r="J194" t="n">
         <v>187249</v>
@@ -18144,7 +18144,7 @@
         <v>26665</v>
       </c>
       <c r="M194" t="n">
-        <v>11.93</v>
+        <v>11.9295</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>148586</v>
       </c>
       <c r="R194" t="n">
-        <v>75.48</v>
+        <v>75.4795</v>
       </c>
       <c r="S194" t="n">
         <v>21469</v>
@@ -18222,7 +18222,7 @@
         <v>1079</v>
       </c>
       <c r="I195" t="n">
-        <v>18.04</v>
+        <v>18.0412</v>
       </c>
       <c r="J195" t="n">
         <v>254927</v>
@@ -18234,7 +18234,7 @@
         <v>39702</v>
       </c>
       <c r="M195" t="n">
-        <v>12.76</v>
+        <v>12.7642</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>216403</v>
       </c>
       <c r="R195" t="n">
-        <v>79.75</v>
+        <v>79.75320000000001</v>
       </c>
       <c r="S195" t="n">
         <v>36462</v>
@@ -18312,7 +18312,7 @@
         <v>1190</v>
       </c>
       <c r="I196" t="n">
-        <v>12.28</v>
+        <v>12.2783</v>
       </c>
       <c r="J196" t="n">
         <v>293687</v>
@@ -18324,7 +18324,7 @@
         <v>27011</v>
       </c>
       <c r="M196" t="n">
-        <v>8.07</v>
+        <v>8.0679</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>255466</v>
       </c>
       <c r="R196" t="n">
-        <v>83</v>
+        <v>83.002</v>
       </c>
       <c r="S196" t="n">
         <v>24213</v>
@@ -18402,7 +18402,7 @@
         <v>1244</v>
       </c>
       <c r="I197" t="n">
-        <v>12.28</v>
+        <v>12.2799</v>
       </c>
       <c r="J197" t="n">
         <v>249282</v>
@@ -18414,7 +18414,7 @@
         <v>24954</v>
       </c>
       <c r="M197" t="n">
-        <v>8.779999999999999</v>
+        <v>8.7811</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>230980</v>
       </c>
       <c r="R197" t="n">
-        <v>89.09999999999999</v>
+        <v>89.1041</v>
       </c>
       <c r="S197" t="n">
         <v>20464</v>
@@ -18492,7 +18492,7 @@
         <v>2439</v>
       </c>
       <c r="I198" t="n">
-        <v>11.28</v>
+        <v>11.2824</v>
       </c>
       <c r="J198" t="n">
         <v>254442</v>
@@ -18504,7 +18504,7 @@
         <v>22659</v>
       </c>
       <c r="M198" t="n">
-        <v>7.9</v>
+        <v>7.9006</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>224048</v>
       </c>
       <c r="R198" t="n">
-        <v>84.81999999999999</v>
+        <v>84.8214</v>
       </c>
       <c r="S198" t="n">
         <v>16749</v>
@@ -18582,7 +18582,7 @@
         <v>2220</v>
       </c>
       <c r="I199" t="n">
-        <v>10.8</v>
+        <v>10.7987</v>
       </c>
       <c r="J199" t="n">
         <v>249035</v>
@@ -18594,7 +18594,7 @@
         <v>24634</v>
       </c>
       <c r="M199" t="n">
-        <v>8.82</v>
+        <v>8.823600000000001</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>217329</v>
       </c>
       <c r="R199" t="n">
-        <v>85.38</v>
+        <v>85.3781</v>
       </c>
       <c r="S199" t="n">
         <v>15558</v>
@@ -18672,7 +18672,7 @@
         <v>2068</v>
       </c>
       <c r="I200" t="n">
-        <v>11.72</v>
+        <v>11.7216</v>
       </c>
       <c r="J200" t="n">
         <v>255981</v>
@@ -18684,7 +18684,7 @@
         <v>26423</v>
       </c>
       <c r="M200" t="n">
-        <v>9.109999999999999</v>
+        <v>9.112299999999999</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>211209</v>
       </c>
       <c r="R200" t="n">
-        <v>80.14</v>
+        <v>80.1409</v>
       </c>
       <c r="S200" t="n">
         <v>15777</v>
@@ -18762,7 +18762,7 @@
         <v>2285</v>
       </c>
       <c r="I201" t="n">
-        <v>8.789999999999999</v>
+        <v>8.7925</v>
       </c>
       <c r="J201" t="n">
         <v>252964</v>
@@ -18774,7 +18774,7 @@
         <v>15719</v>
       </c>
       <c r="M201" t="n">
-        <v>5.67</v>
+        <v>5.6676</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>220628</v>
       </c>
       <c r="R201" t="n">
-        <v>84.33</v>
+        <v>84.3279</v>
       </c>
       <c r="S201" t="n">
         <v>12503</v>
@@ -18852,7 +18852,7 @@
         <v>3014</v>
       </c>
       <c r="I202" t="n">
-        <v>13.11</v>
+        <v>13.1135</v>
       </c>
       <c r="J202" t="n">
         <v>246584</v>
@@ -18864,7 +18864,7 @@
         <v>30154</v>
       </c>
       <c r="M202" t="n">
-        <v>10.63</v>
+        <v>10.6251</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>210574</v>
       </c>
       <c r="R202" t="n">
-        <v>83.02</v>
+        <v>83.0189</v>
       </c>
       <c r="S202" t="n">
         <v>19657</v>
@@ -18942,7 +18942,7 @@
         <v>1340</v>
       </c>
       <c r="I203" t="n">
-        <v>12.66</v>
+        <v>12.6563</v>
       </c>
       <c r="J203" t="n">
         <v>201901</v>
@@ -18954,7 +18954,7 @@
         <v>18937</v>
       </c>
       <c r="M203" t="n">
-        <v>8.19</v>
+        <v>8.192299999999999</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>183020</v>
       </c>
       <c r="R203" t="n">
-        <v>86.23999999999999</v>
+        <v>86.2407</v>
       </c>
       <c r="S203" t="n">
         <v>15528</v>
@@ -19032,7 +19032,7 @@
         <v>1813</v>
       </c>
       <c r="I204" t="n">
-        <v>12.34</v>
+        <v>12.3433</v>
       </c>
       <c r="J204" t="n">
         <v>213665</v>
@@ -19044,7 +19044,7 @@
         <v>21385</v>
       </c>
       <c r="M204" t="n">
-        <v>8.77</v>
+        <v>8.773300000000001</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>193471</v>
       </c>
       <c r="R204" t="n">
-        <v>87.01000000000001</v>
+        <v>87.00530000000001</v>
       </c>
       <c r="S204" t="n">
         <v>15917</v>
@@ -19122,7 +19122,7 @@
         <v>1654</v>
       </c>
       <c r="I205" t="n">
-        <v>9.24</v>
+        <v>9.239100000000001</v>
       </c>
       <c r="J205" t="n">
         <v>218801</v>
@@ -19134,7 +19134,7 @@
         <v>13111</v>
       </c>
       <c r="M205" t="n">
-        <v>5.44</v>
+        <v>5.4386</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>198734</v>
       </c>
       <c r="R205" t="n">
-        <v>87.18000000000001</v>
+        <v>87.1782</v>
       </c>
       <c r="S205" t="n">
         <v>10780</v>
@@ -19212,7 +19212,7 @@
         <v>1150</v>
       </c>
       <c r="I206" t="n">
-        <v>11.99</v>
+        <v>11.9935</v>
       </c>
       <c r="J206" t="n">
         <v>214544</v>
@@ -19224,7 +19224,7 @@
         <v>18321</v>
       </c>
       <c r="M206" t="n">
-        <v>7.52</v>
+        <v>7.5153</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>193517</v>
       </c>
       <c r="R206" t="n">
-        <v>85.83</v>
+        <v>85.8317</v>
       </c>
       <c r="S206" t="n">
         <v>16277</v>
@@ -19302,7 +19302,7 @@
         <v>1570</v>
       </c>
       <c r="I207" t="n">
-        <v>15.62</v>
+        <v>15.6169</v>
       </c>
       <c r="J207" t="n">
         <v>190824</v>
@@ -19314,7 +19314,7 @@
         <v>27524</v>
       </c>
       <c r="M207" t="n">
-        <v>12.17</v>
+        <v>12.1712</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>167832</v>
       </c>
       <c r="R207" t="n">
-        <v>84.5</v>
+        <v>84.50069999999999</v>
       </c>
       <c r="S207" t="n">
         <v>19327</v>
@@ -19392,7 +19392,7 @@
         <v>1362</v>
       </c>
       <c r="I208" t="n">
-        <v>10.46</v>
+        <v>10.4622</v>
       </c>
       <c r="J208" t="n">
         <v>198996</v>
@@ -19404,7 +19404,7 @@
         <v>15751</v>
       </c>
       <c r="M208" t="n">
-        <v>7.09</v>
+        <v>7.0871</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>178413</v>
       </c>
       <c r="R208" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3998</v>
       </c>
       <c r="S208" t="n">
         <v>12024</v>
@@ -19482,7 +19482,7 @@
         <v>1246</v>
       </c>
       <c r="I209" t="n">
-        <v>9.41</v>
+        <v>9.4086</v>
       </c>
       <c r="J209" t="n">
         <v>197790</v>
@@ -19494,7 +19494,7 @@
         <v>14039</v>
       </c>
       <c r="M209" t="n">
-        <v>6.43</v>
+        <v>6.4301</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>181250</v>
       </c>
       <c r="R209" t="n">
-        <v>88.72</v>
+        <v>88.7206</v>
       </c>
       <c r="S209" t="n">
         <v>10884</v>
@@ -19572,7 +19572,7 @@
         <v>1700</v>
       </c>
       <c r="I210" t="n">
-        <v>11.7</v>
+        <v>11.7012</v>
       </c>
       <c r="J210" t="n">
         <v>227237</v>
@@ -19584,7 +19584,7 @@
         <v>23917</v>
       </c>
       <c r="M210" t="n">
-        <v>9.289999999999999</v>
+        <v>9.2936</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>189753</v>
       </c>
       <c r="R210" t="n">
-        <v>81.29000000000001</v>
+        <v>81.288</v>
       </c>
       <c r="S210" t="n">
         <v>17467</v>
@@ -19662,7 +19662,7 @@
         <v>2628</v>
       </c>
       <c r="I211" t="n">
-        <v>9.65</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="J211" t="n">
         <v>273439</v>
@@ -19674,7 +19674,7 @@
         <v>20530</v>
       </c>
       <c r="M211" t="n">
-        <v>6.78</v>
+        <v>6.7834</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>220278</v>
       </c>
       <c r="R211" t="n">
-        <v>78.08</v>
+        <v>78.0793</v>
       </c>
       <c r="S211" t="n">
         <v>12029</v>
@@ -19752,7 +19752,7 @@
         <v>3302</v>
       </c>
       <c r="I212" t="n">
-        <v>7.85</v>
+        <v>7.8524</v>
       </c>
       <c r="J212" t="n">
         <v>301987</v>
@@ -19764,7 +19764,7 @@
         <v>17556</v>
       </c>
       <c r="M212" t="n">
-        <v>5.36</v>
+        <v>5.357</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>237576</v>
       </c>
       <c r="R212" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5967</v>
       </c>
       <c r="S212" t="n">
         <v>8218</v>
@@ -19842,7 +19842,7 @@
         <v>1794</v>
       </c>
       <c r="I213" t="n">
-        <v>10.06</v>
+        <v>10.0649</v>
       </c>
       <c r="J213" t="n">
         <v>288663</v>
@@ -19854,7 +19854,7 @@
         <v>23658</v>
       </c>
       <c r="M213" t="n">
-        <v>7.37</v>
+        <v>7.3708</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>231373</v>
       </c>
       <c r="R213" t="n">
-        <v>77.81999999999999</v>
+        <v>77.82210000000001</v>
       </c>
       <c r="S213" t="n">
         <v>14243</v>
@@ -19932,7 +19932,7 @@
         <v>767</v>
       </c>
       <c r="I214" t="n">
-        <v>7.77</v>
+        <v>7.7686</v>
       </c>
       <c r="J214" t="n">
         <v>197947</v>
@@ -19944,7 +19944,7 @@
         <v>10888</v>
       </c>
       <c r="M214" t="n">
-        <v>5.07</v>
+        <v>5.0732</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>174814</v>
       </c>
       <c r="R214" t="n">
-        <v>85.81</v>
+        <v>85.80589999999999</v>
       </c>
       <c r="S214" t="n">
         <v>7879</v>
@@ -20022,7 +20022,7 @@
         <v>1228</v>
       </c>
       <c r="I215" t="n">
-        <v>17.75</v>
+        <v>17.7516</v>
       </c>
       <c r="J215" t="n">
         <v>236461</v>
@@ -20034,7 +20034,7 @@
         <v>39196</v>
       </c>
       <c r="M215" t="n">
-        <v>13.63</v>
+        <v>13.6336</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>204712</v>
       </c>
       <c r="R215" t="n">
-        <v>82.45</v>
+        <v>82.44540000000001</v>
       </c>
       <c r="S215" t="n">
         <v>33357</v>
@@ -20112,7 +20112,7 @@
         <v>761</v>
       </c>
       <c r="I216" t="n">
-        <v>9.220000000000001</v>
+        <v>9.221399999999999</v>
       </c>
       <c r="J216" t="n">
         <v>222631</v>
@@ -20124,7 +20124,7 @@
         <v>14544</v>
       </c>
       <c r="M216" t="n">
-        <v>5.93</v>
+        <v>5.9304</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>186050</v>
       </c>
       <c r="R216" t="n">
-        <v>80.65000000000001</v>
+        <v>80.6452</v>
       </c>
       <c r="S216" t="n">
         <v>10028</v>
@@ -20202,7 +20202,7 @@
         <v>773</v>
       </c>
       <c r="I217" t="n">
-        <v>9</v>
+        <v>8.9993</v>
       </c>
       <c r="J217" t="n">
         <v>207054</v>
@@ -20214,7 +20214,7 @@
         <v>14645</v>
       </c>
       <c r="M217" t="n">
-        <v>6.44</v>
+        <v>6.4365</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>176421</v>
       </c>
       <c r="R217" t="n">
-        <v>82.87</v>
+        <v>82.8715</v>
       </c>
       <c r="S217" t="n">
         <v>10038</v>
@@ -20292,7 +20292,7 @@
         <v>1256</v>
       </c>
       <c r="I218" t="n">
-        <v>8.880000000000001</v>
+        <v>8.8805</v>
       </c>
       <c r="J218" t="n">
         <v>232536</v>
@@ -20304,7 +20304,7 @@
         <v>14211</v>
       </c>
       <c r="M218" t="n">
-        <v>5.57</v>
+        <v>5.5686</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>196117</v>
       </c>
       <c r="R218" t="n">
-        <v>81.38</v>
+        <v>81.38039999999999</v>
       </c>
       <c r="S218" t="n">
         <v>9548</v>
@@ -20382,7 +20382,7 @@
         <v>1834</v>
       </c>
       <c r="I219" t="n">
-        <v>11.15</v>
+        <v>11.1534</v>
       </c>
       <c r="J219" t="n">
         <v>231529</v>
@@ -20394,7 +20394,7 @@
         <v>20577</v>
       </c>
       <c r="M219" t="n">
-        <v>7.9</v>
+        <v>7.8962</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>194232</v>
       </c>
       <c r="R219" t="n">
-        <v>80.92</v>
+        <v>80.9243</v>
       </c>
       <c r="S219" t="n">
         <v>15711</v>
@@ -20472,7 +20472,7 @@
         <v>1534</v>
       </c>
       <c r="I220" t="n">
-        <v>10.29</v>
+        <v>10.2851</v>
       </c>
       <c r="J220" t="n">
         <v>228521</v>
@@ -20503,7 +20503,7 @@
         <v>196480</v>
       </c>
       <c r="R220" t="n">
-        <v>83.06999999999999</v>
+        <v>83.06699999999999</v>
       </c>
       <c r="S220" t="n">
         <v>12566</v>
@@ -20562,7 +20562,7 @@
         <v>2031</v>
       </c>
       <c r="I221" t="n">
-        <v>12.15</v>
+        <v>12.1456</v>
       </c>
       <c r="J221" t="n">
         <v>221596</v>
@@ -20574,7 +20574,7 @@
         <v>24862</v>
       </c>
       <c r="M221" t="n">
-        <v>9.859999999999999</v>
+        <v>9.8568</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>189795</v>
       </c>
       <c r="R221" t="n">
-        <v>83.47</v>
+        <v>83.4744</v>
       </c>
       <c r="S221" t="n">
         <v>12131</v>
@@ -20652,7 +20652,7 @@
         <v>4120</v>
       </c>
       <c r="I222" t="n">
-        <v>12.21</v>
+        <v>12.2092</v>
       </c>
       <c r="J222" t="n">
         <v>257443</v>
@@ -20664,7 +20664,7 @@
         <v>25729</v>
       </c>
       <c r="M222" t="n">
-        <v>8.77</v>
+        <v>8.773899999999999</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>221951</v>
       </c>
       <c r="R222" t="n">
-        <v>82.97</v>
+        <v>82.9671</v>
       </c>
       <c r="S222" t="n">
         <v>17938</v>
@@ -20742,7 +20742,7 @@
         <v>1801</v>
       </c>
       <c r="I223" t="n">
-        <v>11.47</v>
+        <v>11.4684</v>
       </c>
       <c r="J223" t="n">
         <v>270465</v>
@@ -20754,7 +20754,7 @@
         <v>25916</v>
       </c>
       <c r="M223" t="n">
-        <v>8.48</v>
+        <v>8.4831</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>234987</v>
       </c>
       <c r="R223" t="n">
-        <v>84.05</v>
+        <v>84.0485</v>
       </c>
       <c r="S223" t="n">
         <v>14785</v>
@@ -20832,7 +20832,7 @@
         <v>1093</v>
       </c>
       <c r="I224" t="n">
-        <v>8.99</v>
+        <v>8.994300000000001</v>
       </c>
       <c r="J224" t="n">
         <v>245164</v>
@@ -20844,7 +20844,7 @@
         <v>15986</v>
       </c>
       <c r="M224" t="n">
-        <v>5.93</v>
+        <v>5.9341</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>220857</v>
       </c>
       <c r="R224" t="n">
-        <v>87.15000000000001</v>
+        <v>87.15470000000001</v>
       </c>
       <c r="S224" t="n">
         <v>11236</v>
@@ -20922,7 +20922,7 @@
         <v>2410</v>
       </c>
       <c r="I225" t="n">
-        <v>13.77</v>
+        <v>13.7732</v>
       </c>
       <c r="J225" t="n">
         <v>263685</v>
@@ -20934,7 +20934,7 @@
         <v>32284</v>
       </c>
       <c r="M225" t="n">
-        <v>10.56</v>
+        <v>10.5571</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>218425</v>
       </c>
       <c r="R225" t="n">
-        <v>79.86</v>
+        <v>79.857</v>
       </c>
       <c r="S225" t="n">
         <v>18035</v>
@@ -21012,7 +21012,7 @@
         <v>1750</v>
       </c>
       <c r="I226" t="n">
-        <v>16.31</v>
+        <v>16.3145</v>
       </c>
       <c r="J226" t="n">
         <v>218010</v>
@@ -21024,7 +21024,7 @@
         <v>34797</v>
       </c>
       <c r="M226" t="n">
-        <v>13.36</v>
+        <v>13.3572</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>191195</v>
       </c>
       <c r="R226" t="n">
-        <v>84.70999999999999</v>
+        <v>84.7068</v>
       </c>
       <c r="S226" t="n">
         <v>21885</v>
@@ -21102,7 +21102,7 @@
         <v>1941</v>
       </c>
       <c r="I227" t="n">
-        <v>12.89</v>
+        <v>12.8858</v>
       </c>
       <c r="J227" t="n">
         <v>243762</v>
@@ -21114,7 +21114,7 @@
         <v>24689</v>
       </c>
       <c r="M227" t="n">
-        <v>8.82</v>
+        <v>8.8232</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>180620</v>
       </c>
       <c r="R227" t="n">
-        <v>70.8</v>
+        <v>70.7953</v>
       </c>
       <c r="S227" t="n">
         <v>14124</v>
@@ -21192,7 +21192,7 @@
         <v>3286</v>
       </c>
       <c r="I228" t="n">
-        <v>18.18</v>
+        <v>18.179</v>
       </c>
       <c r="J228" t="n">
         <v>244216</v>
@@ -21204,7 +21204,7 @@
         <v>44056</v>
       </c>
       <c r="M228" t="n">
-        <v>14.76</v>
+        <v>14.7603</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>209419</v>
       </c>
       <c r="R228" t="n">
-        <v>82.31</v>
+        <v>82.31229999999999</v>
       </c>
       <c r="S228" t="n">
         <v>29338</v>
@@ -21282,7 +21282,7 @@
         <v>2613</v>
       </c>
       <c r="I229" t="n">
-        <v>14.62</v>
+        <v>14.621</v>
       </c>
       <c r="J229" t="n">
         <v>233695</v>
@@ -21294,7 +21294,7 @@
         <v>29235</v>
       </c>
       <c r="M229" t="n">
-        <v>10.68</v>
+        <v>10.6808</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>199931</v>
       </c>
       <c r="R229" t="n">
-        <v>81.78</v>
+        <v>81.77809999999999</v>
       </c>
       <c r="S229" t="n">
         <v>22600</v>
@@ -21372,7 +21372,7 @@
         <v>2047</v>
       </c>
       <c r="I230" t="n">
-        <v>9.32</v>
+        <v>9.323700000000001</v>
       </c>
       <c r="J230" t="n">
         <v>274069</v>
@@ -21384,7 +21384,7 @@
         <v>15282</v>
       </c>
       <c r="M230" t="n">
-        <v>5.06</v>
+        <v>5.0561</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>239150</v>
       </c>
       <c r="R230" t="n">
-        <v>83.34</v>
+        <v>83.3368</v>
       </c>
       <c r="S230" t="n">
         <v>14923</v>
@@ -21462,7 +21462,7 @@
         <v>1711</v>
       </c>
       <c r="I231" t="n">
-        <v>10.27</v>
+        <v>10.272</v>
       </c>
       <c r="J231" t="n">
         <v>243329</v>
@@ -21474,7 +21474,7 @@
         <v>14163</v>
       </c>
       <c r="M231" t="n">
-        <v>5.22</v>
+        <v>5.2226</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>196280</v>
       </c>
       <c r="R231" t="n">
-        <v>76.37</v>
+        <v>76.367</v>
       </c>
       <c r="S231" t="n">
         <v>13755</v>
@@ -21552,7 +21552,7 @@
         <v>2207</v>
       </c>
       <c r="I232" t="n">
-        <v>9.17</v>
+        <v>9.1655</v>
       </c>
       <c r="J232" t="n">
         <v>251388</v>
@@ -21564,7 +21564,7 @@
         <v>13306</v>
       </c>
       <c r="M232" t="n">
-        <v>4.81</v>
+        <v>4.8079</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>199013</v>
       </c>
       <c r="R232" t="n">
-        <v>75.54000000000001</v>
+        <v>75.54170000000001</v>
       </c>
       <c r="S232" t="n">
         <v>10819</v>
@@ -21642,7 +21642,7 @@
         <v>1670</v>
       </c>
       <c r="I233" t="n">
-        <v>8.82</v>
+        <v>8.8209</v>
       </c>
       <c r="J233" t="n">
         <v>224140</v>
@@ -21654,7 +21654,7 @@
         <v>11768</v>
       </c>
       <c r="M233" t="n">
-        <v>4.79</v>
+        <v>4.7872</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>180555</v>
       </c>
       <c r="R233" t="n">
-        <v>77.14</v>
+        <v>77.1418</v>
       </c>
       <c r="S233" t="n">
         <v>10572</v>
@@ -21732,7 +21732,7 @@
         <v>1982</v>
       </c>
       <c r="I234" t="n">
-        <v>11.7</v>
+        <v>11.6973</v>
       </c>
       <c r="J234" t="n">
         <v>214360</v>
@@ -21744,7 +21744,7 @@
         <v>17537</v>
       </c>
       <c r="M234" t="n">
-        <v>7.22</v>
+        <v>7.2241</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>174927</v>
       </c>
       <c r="R234" t="n">
-        <v>77.67</v>
+        <v>77.66970000000001</v>
       </c>
       <c r="S234" t="n">
         <v>15139</v>
@@ -21822,7 +21822,7 @@
         <v>2232</v>
       </c>
       <c r="I235" t="n">
-        <v>8.609999999999999</v>
+        <v>8.614599999999999</v>
       </c>
       <c r="J235" t="n">
         <v>232213</v>
@@ -21834,7 +21834,7 @@
         <v>10266</v>
       </c>
       <c r="M235" t="n">
-        <v>4.04</v>
+        <v>4.0401</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>177534</v>
       </c>
       <c r="R235" t="n">
-        <v>72.81</v>
+        <v>72.8085</v>
       </c>
       <c r="S235" t="n">
         <v>9456</v>
@@ -21985,13 +21985,13 @@
         <v>18772</v>
       </c>
       <c r="H2" t="n">
-        <v>35.58</v>
+        <v>35.5837</v>
       </c>
       <c r="I2" t="n">
         <v>2830936</v>
       </c>
       <c r="J2" t="n">
-        <v>29.31</v>
+        <v>29.3096</v>
       </c>
     </row>
     <row r="3">
@@ -22019,13 +22019,13 @@
         <v>23736</v>
       </c>
       <c r="H3" t="n">
-        <v>25.18</v>
+        <v>25.1805</v>
       </c>
       <c r="I3" t="n">
         <v>2260036</v>
       </c>
       <c r="J3" t="n">
-        <v>18.92</v>
+        <v>18.9185</v>
       </c>
     </row>
     <row r="4">
@@ -22053,13 +22053,13 @@
         <v>22401</v>
       </c>
       <c r="H4" t="n">
-        <v>23.06</v>
+        <v>23.0594</v>
       </c>
       <c r="I4" t="n">
         <v>1955283</v>
       </c>
       <c r="J4" t="n">
-        <v>20.03</v>
+        <v>20.027</v>
       </c>
     </row>
     <row r="5">
@@ -22087,13 +22087,13 @@
         <v>23202</v>
       </c>
       <c r="H5" t="n">
-        <v>20.17</v>
+        <v>20.1721</v>
       </c>
       <c r="I5" t="n">
         <v>2696813</v>
       </c>
       <c r="J5" t="n">
-        <v>16.38</v>
+        <v>16.383</v>
       </c>
     </row>
     <row r="6">
@@ -22121,13 +22121,13 @@
         <v>10719</v>
       </c>
       <c r="H6" t="n">
-        <v>19.57</v>
+        <v>19.5743</v>
       </c>
       <c r="I6" t="n">
         <v>1192194</v>
       </c>
       <c r="J6" t="n">
-        <v>14.92</v>
+        <v>14.9161</v>
       </c>
     </row>
     <row r="7">
@@ -22155,13 +22155,13 @@
         <v>20437</v>
       </c>
       <c r="H7" t="n">
-        <v>17.3</v>
+        <v>17.3014</v>
       </c>
       <c r="I7" t="n">
         <v>3157413</v>
       </c>
       <c r="J7" t="n">
-        <v>11.86</v>
+        <v>11.8589</v>
       </c>
     </row>
     <row r="8">
@@ -22189,13 +22189,13 @@
         <v>20182</v>
       </c>
       <c r="H8" t="n">
-        <v>16.8</v>
+        <v>16.7952</v>
       </c>
       <c r="I8" t="n">
         <v>1672075</v>
       </c>
       <c r="J8" t="n">
-        <v>13.56</v>
+        <v>13.5632</v>
       </c>
     </row>
     <row r="9">
@@ -22223,13 +22223,13 @@
         <v>10055</v>
       </c>
       <c r="H9" t="n">
-        <v>16.5</v>
+        <v>16.5019</v>
       </c>
       <c r="I9" t="n">
         <v>1133587</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>13.0038</v>
       </c>
     </row>
     <row r="10">
@@ -22257,13 +22257,13 @@
         <v>13181</v>
       </c>
       <c r="H10" t="n">
-        <v>16.29</v>
+        <v>16.2944</v>
       </c>
       <c r="I10" t="n">
         <v>1740222</v>
       </c>
       <c r="J10" t="n">
-        <v>12.87</v>
+        <v>12.8664</v>
       </c>
     </row>
     <row r="11">
@@ -22291,13 +22291,13 @@
         <v>12000</v>
       </c>
       <c r="H11" t="n">
-        <v>15.16</v>
+        <v>15.1557</v>
       </c>
       <c r="I11" t="n">
         <v>1253264</v>
       </c>
       <c r="J11" t="n">
-        <v>11.64</v>
+        <v>11.6377</v>
       </c>
     </row>
     <row r="12">
@@ -22325,13 +22325,13 @@
         <v>9805</v>
       </c>
       <c r="H12" t="n">
-        <v>14.01</v>
+        <v>14.0056</v>
       </c>
       <c r="I12" t="n">
         <v>2126303</v>
       </c>
       <c r="J12" t="n">
-        <v>10.24</v>
+        <v>10.2435</v>
       </c>
     </row>
     <row r="13">
@@ -22359,13 +22359,13 @@
         <v>11336</v>
       </c>
       <c r="H13" t="n">
-        <v>13.88</v>
+        <v>13.8827</v>
       </c>
       <c r="I13" t="n">
         <v>2466954</v>
       </c>
       <c r="J13" t="n">
-        <v>9.99</v>
+        <v>9.985900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -22393,13 +22393,13 @@
         <v>6875</v>
       </c>
       <c r="H14" t="n">
-        <v>13.72</v>
+        <v>13.7238</v>
       </c>
       <c r="I14" t="n">
         <v>944701</v>
       </c>
       <c r="J14" t="n">
-        <v>10.68</v>
+        <v>10.6835</v>
       </c>
     </row>
     <row r="15">
@@ -22427,13 +22427,13 @@
         <v>8636</v>
       </c>
       <c r="H15" t="n">
-        <v>13.21</v>
+        <v>13.2073</v>
       </c>
       <c r="I15" t="n">
         <v>1310951</v>
       </c>
       <c r="J15" t="n">
-        <v>10.62</v>
+        <v>10.6166</v>
       </c>
     </row>
     <row r="16">
@@ -22461,13 +22461,13 @@
         <v>6353</v>
       </c>
       <c r="H16" t="n">
-        <v>12.26</v>
+        <v>12.2631</v>
       </c>
       <c r="I16" t="n">
         <v>1110599</v>
       </c>
       <c r="J16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.702500000000001</v>
       </c>
     </row>
     <row r="17">
@@ -22495,13 +22495,13 @@
         <v>5350</v>
       </c>
       <c r="H17" t="n">
-        <v>12.04</v>
+        <v>12.0382</v>
       </c>
       <c r="I17" t="n">
         <v>979652</v>
       </c>
       <c r="J17" t="n">
-        <v>8.92</v>
+        <v>8.9185</v>
       </c>
     </row>
     <row r="18">
@@ -22529,13 +22529,13 @@
         <v>20171</v>
       </c>
       <c r="H18" t="n">
-        <v>11.96</v>
+        <v>11.9592</v>
       </c>
       <c r="I18" t="n">
         <v>2755830</v>
       </c>
       <c r="J18" t="n">
-        <v>9.06</v>
+        <v>9.0646</v>
       </c>
     </row>
     <row r="19">
@@ -22563,13 +22563,13 @@
         <v>10527</v>
       </c>
       <c r="H19" t="n">
-        <v>11.88</v>
+        <v>11.8838</v>
       </c>
       <c r="I19" t="n">
         <v>1919159</v>
       </c>
       <c r="J19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5548</v>
       </c>
     </row>
     <row r="20">
@@ -22597,13 +22597,13 @@
         <v>9295</v>
       </c>
       <c r="H20" t="n">
-        <v>11.68</v>
+        <v>11.6808</v>
       </c>
       <c r="I20" t="n">
         <v>911599</v>
       </c>
       <c r="J20" t="n">
-        <v>8.789999999999999</v>
+        <v>8.7864</v>
       </c>
     </row>
     <row r="21">
@@ -22631,13 +22631,13 @@
         <v>10135</v>
       </c>
       <c r="H21" t="n">
-        <v>11.68</v>
+        <v>11.6794</v>
       </c>
       <c r="I21" t="n">
         <v>1497417</v>
       </c>
       <c r="J21" t="n">
-        <v>7.94</v>
+        <v>7.9354</v>
       </c>
     </row>
     <row r="22">
@@ -22665,13 +22665,13 @@
         <v>10844</v>
       </c>
       <c r="H22" t="n">
-        <v>11.25</v>
+        <v>11.2519</v>
       </c>
       <c r="I22" t="n">
         <v>2015796</v>
       </c>
       <c r="J22" t="n">
-        <v>8.1</v>
+        <v>8.1046</v>
       </c>
     </row>
     <row r="23">
@@ -22699,13 +22699,13 @@
         <v>9587</v>
       </c>
       <c r="H23" t="n">
-        <v>11.12</v>
+        <v>11.1244</v>
       </c>
       <c r="I23" t="n">
         <v>1033373</v>
       </c>
       <c r="J23" t="n">
-        <v>8.58</v>
+        <v>8.5756</v>
       </c>
     </row>
     <row r="24">
@@ -22733,13 +22733,13 @@
         <v>10579</v>
       </c>
       <c r="H24" t="n">
-        <v>11.05</v>
+        <v>11.0467</v>
       </c>
       <c r="I24" t="n">
         <v>1264411</v>
       </c>
       <c r="J24" t="n">
-        <v>8.050000000000001</v>
+        <v>8.0489</v>
       </c>
     </row>
     <row r="25">
@@ -22767,13 +22767,13 @@
         <v>6619</v>
       </c>
       <c r="H25" t="n">
-        <v>10.9</v>
+        <v>10.9028</v>
       </c>
       <c r="I25" t="n">
         <v>1376624</v>
       </c>
       <c r="J25" t="n">
-        <v>7.65</v>
+        <v>7.6516</v>
       </c>
     </row>
     <row r="26">
@@ -22801,13 +22801,13 @@
         <v>7998</v>
       </c>
       <c r="H26" t="n">
-        <v>10.59</v>
+        <v>10.5856</v>
       </c>
       <c r="I26" t="n">
         <v>1586653</v>
       </c>
       <c r="J26" t="n">
-        <v>8.15</v>
+        <v>8.152699999999999</v>
       </c>
     </row>
     <row r="27">
@@ -22835,13 +22835,13 @@
         <v>10652</v>
       </c>
       <c r="H27" t="n">
-        <v>10.39</v>
+        <v>10.386</v>
       </c>
       <c r="I27" t="n">
         <v>1554040</v>
       </c>
       <c r="J27" t="n">
-        <v>7.53</v>
+        <v>7.5321</v>
       </c>
     </row>
     <row r="28">
@@ -22869,13 +22869,13 @@
         <v>3248</v>
       </c>
       <c r="H28" t="n">
-        <v>10.1</v>
+        <v>10.0995</v>
       </c>
       <c r="I28" t="n">
         <v>527947</v>
       </c>
       <c r="J28" t="n">
-        <v>7.01</v>
+        <v>7.0074</v>
       </c>
     </row>
     <row r="29">
@@ -22903,13 +22903,13 @@
         <v>8947</v>
       </c>
       <c r="H29" t="n">
-        <v>10.01</v>
+        <v>10.0126</v>
       </c>
       <c r="I29" t="n">
         <v>1298907</v>
       </c>
       <c r="J29" t="n">
-        <v>6.83</v>
+        <v>6.8291</v>
       </c>
     </row>
     <row r="30">
@@ -22937,13 +22937,13 @@
         <v>7989</v>
       </c>
       <c r="H30" t="n">
-        <v>9.84</v>
+        <v>9.840199999999999</v>
       </c>
       <c r="I30" t="n">
         <v>1951445</v>
       </c>
       <c r="J30" t="n">
-        <v>7.01</v>
+        <v>7.0103</v>
       </c>
     </row>
     <row r="31">
@@ -22977,7 +22977,7 @@
         <v>1123029</v>
       </c>
       <c r="J31" t="n">
-        <v>7.09</v>
+        <v>7.0871</v>
       </c>
     </row>
     <row r="32">
@@ -23005,13 +23005,13 @@
         <v>11849</v>
       </c>
       <c r="H32" t="n">
-        <v>9.630000000000001</v>
+        <v>9.6287</v>
       </c>
       <c r="I32" t="n">
         <v>1510550</v>
       </c>
       <c r="J32" t="n">
-        <v>5.17</v>
+        <v>5.1681</v>
       </c>
     </row>
     <row r="33">
@@ -23039,13 +23039,13 @@
         <v>4137</v>
       </c>
       <c r="H33" t="n">
-        <v>9.619999999999999</v>
+        <v>9.620699999999999</v>
       </c>
       <c r="I33" t="n">
         <v>729216</v>
       </c>
       <c r="J33" t="n">
-        <v>6.93</v>
+        <v>6.9284</v>
       </c>
     </row>
     <row r="34">
@@ -23073,13 +23073,13 @@
         <v>3292</v>
       </c>
       <c r="H34" t="n">
-        <v>9.52</v>
+        <v>9.5204</v>
       </c>
       <c r="I34" t="n">
         <v>547133</v>
       </c>
       <c r="J34" t="n">
-        <v>7.13</v>
+        <v>7.1345</v>
       </c>
     </row>
     <row r="35">
@@ -23107,13 +23107,13 @@
         <v>2295</v>
       </c>
       <c r="H35" t="n">
-        <v>8.869999999999999</v>
+        <v>8.8706</v>
       </c>
       <c r="I35" t="n">
         <v>845164</v>
       </c>
       <c r="J35" t="n">
-        <v>5.92</v>
+        <v>5.9217</v>
       </c>
     </row>
     <row r="36">
@@ -23141,13 +23141,13 @@
         <v>3526</v>
       </c>
       <c r="H36" t="n">
-        <v>8.390000000000001</v>
+        <v>8.391</v>
       </c>
       <c r="I36" t="n">
         <v>555131</v>
       </c>
       <c r="J36" t="n">
-        <v>5.99</v>
+        <v>5.9881</v>
       </c>
     </row>
     <row r="37">
@@ -23175,13 +23175,13 @@
         <v>5709</v>
       </c>
       <c r="H37" t="n">
-        <v>7.27</v>
+        <v>7.2659</v>
       </c>
       <c r="I37" t="n">
         <v>1109911</v>
       </c>
       <c r="J37" t="n">
-        <v>4.37</v>
+        <v>4.3681</v>
       </c>
     </row>
     <row r="38">
@@ -23209,13 +23209,13 @@
         <v>6903</v>
       </c>
       <c r="H38" t="n">
-        <v>6.34</v>
+        <v>6.3414</v>
       </c>
       <c r="I38" t="n">
         <v>1240108</v>
       </c>
       <c r="J38" t="n">
-        <v>3.53</v>
+        <v>3.526</v>
       </c>
     </row>
     <row r="39">
@@ -23249,7 +23249,7 @@
         <v>522954</v>
       </c>
       <c r="J39" t="n">
-        <v>1.49</v>
+        <v>1.4948</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/tamil-nadu.xlsx
+++ b/downloads/tamil-nadu.xlsx
@@ -60889,7 +60889,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jan2025 less the draft. It counts ten months of ordinary changes as well as the revision, so it is not the names removed.</t>
+          <t>jan2025 less the draft. It counts ten months of ordinary changes as well as the revision, so it is a different count from the names left off.</t>
         </is>
       </c>
     </row>
